--- a/linux.xlsx
+++ b/linux.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/F3F5AF62C6A6F1DD/المستندات/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2567" documentId="8_{25755E88-947E-4243-A6E5-7305260DAEDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F94DD2F5-CF91-484D-8C9F-6D7E0D0BCEF1}"/>
+  <xr:revisionPtr revIDLastSave="2584" documentId="8_{25755E88-947E-4243-A6E5-7305260DAEDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B73F3373-F559-45F9-88EF-50617241F66D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="916" xr2:uid="{81EB0F92-22DA-4355-B1D5-1D0795525769}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4996" uniqueCount="4514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5022" uniqueCount="4540">
   <si>
     <t>centos</t>
   </si>
@@ -25549,6 +25549,103 @@
   </si>
   <si>
     <t>طريقة استعمال الأداة</t>
+  </si>
+  <si>
+    <t>Aireplay-ng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">مخصصه لقطع الاتصال بين الجهاز والروتر </t>
+  </si>
+  <si>
+    <t>الهجمات التي يمكن استخدامه بـAireplay-ng</t>
+  </si>
+  <si>
+    <t>Attack 0: Deauthentication</t>
+  </si>
+  <si>
+    <t>Attack 1: Fake authentication</t>
+  </si>
+  <si>
+    <t>Attack 2: Interactive packet replay</t>
+  </si>
+  <si>
+    <t>Attack 3: ARP request replay attack</t>
+  </si>
+  <si>
+    <t>Attack 4: KoreK chopchop attack</t>
+  </si>
+  <si>
+    <t>Attack 5: Fragmentation attack</t>
+  </si>
+  <si>
+    <t>Attack 6: Cafe-latte attack</t>
+  </si>
+  <si>
+    <t>Attack 7: Client-oriented fragmentation attack</t>
+  </si>
+  <si>
+    <t>Attack 8: WPA Migration Mode</t>
+  </si>
+  <si>
+    <t>Attack 9: Injection test</t>
+  </si>
+  <si>
+    <t>هجوم يعتمد على إرسال إطارات فصل (Deauth Frames) إلى جهاز أو نقطة وصول.
+يعني يخلي الجهاز يفصل من الشبكة</t>
+  </si>
+  <si>
+    <t>محاولة تسجيل دخول وهمي إلى نقطة الوصول في شبكات WEP القديمة</t>
+  </si>
+  <si>
+    <t>إعادة إرسال حزم يتم التقاطها بشكل تفاعلي</t>
+  </si>
+  <si>
+    <t>إعادة إرسال حزم ARP في شبكات WEP</t>
+  </si>
+  <si>
+    <t>هجوم قديم على WEP يعتمد على تعديل بايت واحد من الحزمة</t>
+  </si>
+  <si>
+    <t>هجوم تجزئة على WEP.</t>
+  </si>
+  <si>
+    <t>هجوم على العميل وليس على نقطة الوصول</t>
+  </si>
+  <si>
+    <t>نسخة مطوّرة من هجوم التجزئة ولكن موجهة للعميل</t>
+  </si>
+  <si>
+    <t>اختبار خاص بالشبكات التي تدعم WPA + WEP معًا</t>
+  </si>
+  <si>
+    <t>اختبار قدرة بطاقة الشبكة على حقن الحزم.</t>
+  </si>
+  <si>
+    <t>الأوامر الخاصه بهجمة  Deauthentication</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> aireplay-ng
+ -0
+ 1
+ -a 
+00:14:6C:7E:40:80
+ -c 
+00:0F:B5:34:30:30 
+ath0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> aireplay-ng
+وهذا هو الامر الأساسي 
+-0
+يعني نوع الهجمة ارجع للسطر 218
+1
+عدد مجموعات الهجمات و الأفضل تحط صفر علشان مايوقف
+-a
+عنوان الماك حق الروتر 
+-c
+عنوان MAC لجهاز معيّن متصل بروتر
+ath0
+اسم اللاقط في جهازك</t>
   </si>
 </sst>
 </file>
@@ -25985,7 +26082,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="223">
+  <cellXfs count="226">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -26520,6 +26617,15 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -28600,10 +28706,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="185" t="s">
+      <c r="A1" s="188" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="185"/>
+      <c r="B1" s="188"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="116" t="s">
@@ -28638,20 +28744,20 @@
       <c r="B6" s="96"/>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="187" t="s">
+      <c r="A7" s="190" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="187"/>
+      <c r="B7" s="190"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="95"/>
       <c r="B8" s="95"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="184" t="s">
+      <c r="A9" s="187" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="184"/>
+      <c r="B9" s="187"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="116" t="s">
@@ -28663,7 +28769,7 @@
     </row>
     <row r="11" spans="1:5" ht="15.6" customHeight="1">
       <c r="A11" s="109">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B11" s="97"/>
       <c r="D11" s="112" t="s">
@@ -28677,10 +28783,10 @@
       <c r="D12" s="76"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="184" t="s">
+      <c r="A13" s="187" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="184"/>
+      <c r="B13" s="187"/>
       <c r="D13" s="79"/>
     </row>
     <row r="14" spans="1:5">
@@ -28694,7 +28800,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="109">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B15" s="9"/>
       <c r="D15" s="80"/>
@@ -28705,10 +28811,10 @@
       <c r="D16" s="80"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="185" t="s">
+      <c r="A17" s="188" t="s">
         <v>11</v>
       </c>
-      <c r="B17" s="185"/>
+      <c r="B17" s="188"/>
       <c r="D17" s="81"/>
       <c r="E17" s="157"/>
     </row>
@@ -28723,10 +28829,10 @@
       <c r="E18" s="158"/>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="186" t="s">
+      <c r="A19" s="189" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="186"/>
+      <c r="B19" s="189"/>
       <c r="D19" s="76"/>
       <c r="E19" s="92"/>
     </row>
@@ -28735,10 +28841,10 @@
       <c r="D20" s="81"/>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="183" t="s">
+      <c r="A21" s="186" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="183"/>
+      <c r="B21" s="186"/>
       <c r="D21" s="81"/>
     </row>
     <row r="22" spans="1:5">
@@ -28760,10 +28866,10 @@
       <c r="D24" s="81"/>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="183" t="s">
+      <c r="A25" s="186" t="s">
         <v>4501</v>
       </c>
-      <c r="B25" s="183"/>
+      <c r="B25" s="186"/>
       <c r="D25" s="81"/>
     </row>
     <row r="26" spans="1:5">
@@ -29612,11 +29718,11 @@
       <c r="C1" s="110"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="189" t="s">
+      <c r="A2" s="192" t="s">
         <v>3659</v>
       </c>
-      <c r="B2" s="189"/>
-      <c r="C2" s="189"/>
+      <c r="B2" s="192"/>
+      <c r="C2" s="192"/>
     </row>
     <row r="3" spans="1:3" ht="45">
       <c r="A3" s="122" t="s">
@@ -29630,10 +29736,10 @@
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="218" t="s">
+      <c r="A4" s="221" t="s">
         <v>3663</v>
       </c>
-      <c r="B4" s="190" t="s">
+      <c r="B4" s="193" t="s">
         <v>3664</v>
       </c>
       <c r="C4" s="112" t="s">
@@ -29641,24 +29747,24 @@
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="218"/>
-      <c r="B5" s="190"/>
+      <c r="A5" s="221"/>
+      <c r="B5" s="193"/>
       <c r="C5" s="23" t="s">
         <v>3666</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="218"/>
-      <c r="B6" s="190"/>
+      <c r="A6" s="221"/>
+      <c r="B6" s="193"/>
       <c r="C6" s="23" t="s">
         <v>3667</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.65" customHeight="1">
-      <c r="A7" s="218" t="s">
+      <c r="A7" s="221" t="s">
         <v>3668</v>
       </c>
-      <c r="B7" s="190" t="s">
+      <c r="B7" s="193" t="s">
         <v>3669</v>
       </c>
       <c r="C7" s="23" t="s">
@@ -29666,17 +29772,17 @@
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="218"/>
-      <c r="B8" s="190"/>
+      <c r="A8" s="221"/>
+      <c r="B8" s="193"/>
       <c r="C8" s="23" t="s">
         <v>3671</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30">
-      <c r="A9" s="218" t="s">
+      <c r="A9" s="221" t="s">
         <v>3672</v>
       </c>
-      <c r="B9" s="190" t="s">
+      <c r="B9" s="193" t="s">
         <v>3673</v>
       </c>
       <c r="C9" s="112" t="s">
@@ -29684,31 +29790,31 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="25.5">
-      <c r="A10" s="218"/>
-      <c r="B10" s="190"/>
+      <c r="A10" s="221"/>
+      <c r="B10" s="193"/>
       <c r="C10" s="23" t="s">
         <v>3675</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="218"/>
-      <c r="B11" s="190"/>
+      <c r="A11" s="221"/>
+      <c r="B11" s="193"/>
       <c r="C11" s="112" t="s">
         <v>3676</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="218"/>
-      <c r="B12" s="190"/>
+      <c r="A12" s="221"/>
+      <c r="B12" s="193"/>
       <c r="C12" s="23" t="s">
         <v>3666</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="218" t="s">
+      <c r="A13" s="221" t="s">
         <v>3677</v>
       </c>
-      <c r="B13" s="190" t="s">
+      <c r="B13" s="193" t="s">
         <v>3678</v>
       </c>
       <c r="C13" s="112" t="s">
@@ -29716,17 +29822,17 @@
       </c>
     </row>
     <row r="14" spans="1:3" ht="63.75">
-      <c r="A14" s="218"/>
-      <c r="B14" s="190"/>
+      <c r="A14" s="221"/>
+      <c r="B14" s="193"/>
       <c r="C14" s="23" t="s">
         <v>3680</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="218" t="s">
+      <c r="A15" s="221" t="s">
         <v>3681</v>
       </c>
-      <c r="B15" s="190" t="s">
+      <c r="B15" s="193" t="s">
         <v>3682</v>
       </c>
       <c r="C15" s="112" t="s">
@@ -29734,15 +29840,15 @@
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="218"/>
-      <c r="B16" s="190"/>
+      <c r="A16" s="221"/>
+      <c r="B16" s="193"/>
       <c r="C16" s="23" t="s">
         <v>3684</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="218"/>
-      <c r="B17" s="190"/>
+      <c r="A17" s="221"/>
+      <c r="B17" s="193"/>
       <c r="C17" s="112" t="s">
         <v>3685</v>
       </c>
@@ -29754,8 +29860,8 @@
       <c r="I17" s="112"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="218"/>
-      <c r="B18" s="190"/>
+      <c r="A18" s="221"/>
+      <c r="B18" s="193"/>
       <c r="C18" s="23" t="s">
         <v>3686</v>
       </c>
@@ -29784,10 +29890,10 @@
       <c r="I19" s="112"/>
     </row>
     <row r="20" spans="1:9" ht="30">
-      <c r="A20" s="218" t="s">
+      <c r="A20" s="221" t="s">
         <v>3690</v>
       </c>
-      <c r="B20" s="190" t="s">
+      <c r="B20" s="193" t="s">
         <v>3691</v>
       </c>
       <c r="C20" s="112" t="s">
@@ -29801,8 +29907,8 @@
       <c r="I20" s="112"/>
     </row>
     <row r="21" spans="1:9" ht="25.5">
-      <c r="A21" s="218"/>
-      <c r="B21" s="190"/>
+      <c r="A21" s="221"/>
+      <c r="B21" s="193"/>
       <c r="C21" s="23" t="s">
         <v>3693</v>
       </c>
@@ -29869,118 +29975,118 @@
       <c r="B26" s="112"/>
       <c r="C26" s="112"/>
       <c r="D26" s="112"/>
-      <c r="E26" s="220" t="s">
+      <c r="E26" s="223" t="s">
         <v>3703</v>
       </c>
-      <c r="F26" s="220"/>
-      <c r="G26" s="220"/>
-      <c r="H26" s="220"/>
-      <c r="I26" s="220"/>
+      <c r="F26" s="223"/>
+      <c r="G26" s="223"/>
+      <c r="H26" s="223"/>
+      <c r="I26" s="223"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="112"/>
       <c r="B27" s="112"/>
       <c r="C27" s="112"/>
       <c r="D27" s="112"/>
-      <c r="E27" s="220"/>
-      <c r="F27" s="220"/>
-      <c r="G27" s="220"/>
-      <c r="H27" s="220"/>
-      <c r="I27" s="220"/>
+      <c r="E27" s="223"/>
+      <c r="F27" s="223"/>
+      <c r="G27" s="223"/>
+      <c r="H27" s="223"/>
+      <c r="I27" s="223"/>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="221" t="s">
+      <c r="A28" s="224" t="s">
         <v>3704</v>
       </c>
-      <c r="B28" s="221"/>
-      <c r="C28" s="221"/>
+      <c r="B28" s="224"/>
+      <c r="C28" s="224"/>
       <c r="D28" s="112"/>
-      <c r="E28" s="220"/>
-      <c r="F28" s="220"/>
-      <c r="G28" s="220"/>
-      <c r="H28" s="220"/>
-      <c r="I28" s="220"/>
+      <c r="E28" s="223"/>
+      <c r="F28" s="223"/>
+      <c r="G28" s="223"/>
+      <c r="H28" s="223"/>
+      <c r="I28" s="223"/>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="112"/>
       <c r="B29" s="112"/>
       <c r="C29" s="112"/>
       <c r="D29" s="112"/>
-      <c r="E29" s="220"/>
-      <c r="F29" s="220"/>
-      <c r="G29" s="220"/>
-      <c r="H29" s="220"/>
-      <c r="I29" s="220"/>
+      <c r="E29" s="223"/>
+      <c r="F29" s="223"/>
+      <c r="G29" s="223"/>
+      <c r="H29" s="223"/>
+      <c r="I29" s="223"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="112"/>
       <c r="B30" s="112"/>
       <c r="C30" s="112"/>
       <c r="D30" s="112"/>
-      <c r="E30" s="220"/>
-      <c r="F30" s="220"/>
-      <c r="G30" s="220"/>
-      <c r="H30" s="220"/>
-      <c r="I30" s="220"/>
+      <c r="E30" s="223"/>
+      <c r="F30" s="223"/>
+      <c r="G30" s="223"/>
+      <c r="H30" s="223"/>
+      <c r="I30" s="223"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="112"/>
       <c r="B31" s="112"/>
       <c r="C31" s="112"/>
       <c r="D31" s="112"/>
-      <c r="E31" s="220"/>
-      <c r="F31" s="220"/>
-      <c r="G31" s="220"/>
-      <c r="H31" s="220"/>
-      <c r="I31" s="220"/>
+      <c r="E31" s="223"/>
+      <c r="F31" s="223"/>
+      <c r="G31" s="223"/>
+      <c r="H31" s="223"/>
+      <c r="I31" s="223"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="112"/>
       <c r="B32" s="112"/>
       <c r="C32" s="112"/>
       <c r="D32" s="112"/>
-      <c r="E32" s="220"/>
-      <c r="F32" s="220"/>
-      <c r="G32" s="220"/>
-      <c r="H32" s="220"/>
-      <c r="I32" s="220"/>
+      <c r="E32" s="223"/>
+      <c r="F32" s="223"/>
+      <c r="G32" s="223"/>
+      <c r="H32" s="223"/>
+      <c r="I32" s="223"/>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="189" t="s">
+      <c r="A33" s="192" t="s">
         <v>3705</v>
       </c>
-      <c r="B33" s="189"/>
-      <c r="C33" s="189"/>
+      <c r="B33" s="192"/>
+      <c r="C33" s="192"/>
       <c r="D33" s="112"/>
-      <c r="E33" s="220"/>
-      <c r="F33" s="220"/>
-      <c r="G33" s="220"/>
-      <c r="H33" s="220"/>
-      <c r="I33" s="220"/>
+      <c r="E33" s="223"/>
+      <c r="F33" s="223"/>
+      <c r="G33" s="223"/>
+      <c r="H33" s="223"/>
+      <c r="I33" s="223"/>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="112"/>
       <c r="B34" s="112"/>
       <c r="C34" s="112"/>
       <c r="D34" s="112"/>
-      <c r="E34" s="220"/>
-      <c r="F34" s="220"/>
-      <c r="G34" s="220"/>
-      <c r="H34" s="220"/>
-      <c r="I34" s="220"/>
+      <c r="E34" s="223"/>
+      <c r="F34" s="223"/>
+      <c r="G34" s="223"/>
+      <c r="H34" s="223"/>
+      <c r="I34" s="223"/>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="188" t="s">
+      <c r="A35" s="191" t="s">
         <v>3706</v>
       </c>
-      <c r="B35" s="188"/>
-      <c r="C35" s="188"/>
+      <c r="B35" s="191"/>
+      <c r="C35" s="191"/>
       <c r="D35" s="112"/>
-      <c r="E35" s="220"/>
-      <c r="F35" s="220"/>
-      <c r="G35" s="220"/>
-      <c r="H35" s="220"/>
-      <c r="I35" s="220"/>
+      <c r="E35" s="223"/>
+      <c r="F35" s="223"/>
+      <c r="G35" s="223"/>
+      <c r="H35" s="223"/>
+      <c r="I35" s="223"/>
     </row>
     <row r="36" spans="1:9" ht="30">
       <c r="A36" s="112"/>
@@ -29989,24 +30095,24 @@
       </c>
       <c r="C36" s="112"/>
       <c r="D36" s="112"/>
-      <c r="E36" s="220"/>
-      <c r="F36" s="220"/>
-      <c r="G36" s="220"/>
-      <c r="H36" s="220"/>
-      <c r="I36" s="220"/>
+      <c r="E36" s="223"/>
+      <c r="F36" s="223"/>
+      <c r="G36" s="223"/>
+      <c r="H36" s="223"/>
+      <c r="I36" s="223"/>
     </row>
     <row r="37" spans="1:9" s="65" customFormat="1">
-      <c r="A37" s="217" t="s">
+      <c r="A37" s="220" t="s">
         <v>3708</v>
       </c>
-      <c r="B37" s="217"/>
-      <c r="C37" s="217"/>
+      <c r="B37" s="220"/>
+      <c r="C37" s="220"/>
       <c r="D37" s="112"/>
-      <c r="E37" s="220"/>
-      <c r="F37" s="220"/>
-      <c r="G37" s="220"/>
-      <c r="H37" s="220"/>
-      <c r="I37" s="220"/>
+      <c r="E37" s="223"/>
+      <c r="F37" s="223"/>
+      <c r="G37" s="223"/>
+      <c r="H37" s="223"/>
+      <c r="I37" s="223"/>
     </row>
     <row r="38" spans="1:9" ht="28.9" customHeight="1">
       <c r="A38" s="111" t="s">
@@ -30017,11 +30123,11 @@
       </c>
       <c r="C38" s="112"/>
       <c r="D38" s="112"/>
-      <c r="E38" s="220"/>
-      <c r="F38" s="220"/>
-      <c r="G38" s="220"/>
-      <c r="H38" s="220"/>
-      <c r="I38" s="220"/>
+      <c r="E38" s="223"/>
+      <c r="F38" s="223"/>
+      <c r="G38" s="223"/>
+      <c r="H38" s="223"/>
+      <c r="I38" s="223"/>
     </row>
     <row r="39" spans="1:9" ht="45">
       <c r="A39" s="41" t="s">
@@ -30032,11 +30138,11 @@
       </c>
       <c r="C39" s="112"/>
       <c r="D39" s="112"/>
-      <c r="E39" s="220"/>
-      <c r="F39" s="220"/>
-      <c r="G39" s="220"/>
-      <c r="H39" s="220"/>
-      <c r="I39" s="220"/>
+      <c r="E39" s="223"/>
+      <c r="F39" s="223"/>
+      <c r="G39" s="223"/>
+      <c r="H39" s="223"/>
+      <c r="I39" s="223"/>
     </row>
     <row r="40" spans="1:9" ht="45">
       <c r="A40" s="41" t="s">
@@ -30047,11 +30153,11 @@
       </c>
       <c r="C40" s="112"/>
       <c r="D40" s="112"/>
-      <c r="E40" s="220"/>
-      <c r="F40" s="220"/>
-      <c r="G40" s="220"/>
-      <c r="H40" s="220"/>
-      <c r="I40" s="220"/>
+      <c r="E40" s="223"/>
+      <c r="F40" s="223"/>
+      <c r="G40" s="223"/>
+      <c r="H40" s="223"/>
+      <c r="I40" s="223"/>
     </row>
     <row r="41" spans="1:9" ht="45">
       <c r="A41" s="41" t="s">
@@ -30062,11 +30168,11 @@
       </c>
       <c r="C41" s="112"/>
       <c r="D41" s="112"/>
-      <c r="E41" s="220"/>
-      <c r="F41" s="220"/>
-      <c r="G41" s="220"/>
-      <c r="H41" s="220"/>
-      <c r="I41" s="220"/>
+      <c r="E41" s="223"/>
+      <c r="F41" s="223"/>
+      <c r="G41" s="223"/>
+      <c r="H41" s="223"/>
+      <c r="I41" s="223"/>
     </row>
     <row r="42" spans="1:9" ht="30">
       <c r="A42" s="41" t="s">
@@ -30077,11 +30183,11 @@
       </c>
       <c r="C42" s="112"/>
       <c r="D42" s="112"/>
-      <c r="E42" s="220"/>
-      <c r="F42" s="220"/>
-      <c r="G42" s="220"/>
-      <c r="H42" s="220"/>
-      <c r="I42" s="220"/>
+      <c r="E42" s="223"/>
+      <c r="F42" s="223"/>
+      <c r="G42" s="223"/>
+      <c r="H42" s="223"/>
+      <c r="I42" s="223"/>
     </row>
     <row r="43" spans="1:9" ht="30">
       <c r="A43" s="41" t="s">
@@ -30092,11 +30198,11 @@
       </c>
       <c r="C43" s="112"/>
       <c r="D43" s="112"/>
-      <c r="E43" s="220"/>
-      <c r="F43" s="220"/>
-      <c r="G43" s="220"/>
-      <c r="H43" s="220"/>
-      <c r="I43" s="220"/>
+      <c r="E43" s="223"/>
+      <c r="F43" s="223"/>
+      <c r="G43" s="223"/>
+      <c r="H43" s="223"/>
+      <c r="I43" s="223"/>
     </row>
     <row r="44" spans="1:9" ht="30">
       <c r="A44" s="41" t="s">
@@ -30107,11 +30213,11 @@
       </c>
       <c r="C44" s="112"/>
       <c r="D44" s="112"/>
-      <c r="E44" s="220"/>
-      <c r="F44" s="220"/>
-      <c r="G44" s="220"/>
-      <c r="H44" s="220"/>
-      <c r="I44" s="220"/>
+      <c r="E44" s="223"/>
+      <c r="F44" s="223"/>
+      <c r="G44" s="223"/>
+      <c r="H44" s="223"/>
+      <c r="I44" s="223"/>
     </row>
     <row r="45" spans="1:9" ht="45">
       <c r="A45" s="41" t="s">
@@ -30122,11 +30228,11 @@
       </c>
       <c r="C45" s="112"/>
       <c r="D45" s="112"/>
-      <c r="E45" s="220"/>
-      <c r="F45" s="220"/>
-      <c r="G45" s="220"/>
-      <c r="H45" s="220"/>
-      <c r="I45" s="220"/>
+      <c r="E45" s="223"/>
+      <c r="F45" s="223"/>
+      <c r="G45" s="223"/>
+      <c r="H45" s="223"/>
+      <c r="I45" s="223"/>
     </row>
     <row r="46" spans="1:9" ht="43.15" customHeight="1">
       <c r="A46" s="41" t="s">
@@ -30137,11 +30243,11 @@
       </c>
       <c r="C46" s="112"/>
       <c r="D46" s="112"/>
-      <c r="E46" s="220"/>
-      <c r="F46" s="220"/>
-      <c r="G46" s="220"/>
-      <c r="H46" s="220"/>
-      <c r="I46" s="220"/>
+      <c r="E46" s="223"/>
+      <c r="F46" s="223"/>
+      <c r="G46" s="223"/>
+      <c r="H46" s="223"/>
+      <c r="I46" s="223"/>
     </row>
     <row r="47" spans="1:9" ht="30">
       <c r="A47" s="41" t="s">
@@ -30152,11 +30258,11 @@
       </c>
       <c r="C47" s="112"/>
       <c r="D47" s="112"/>
-      <c r="E47" s="220"/>
-      <c r="F47" s="220"/>
-      <c r="G47" s="220"/>
-      <c r="H47" s="220"/>
-      <c r="I47" s="220"/>
+      <c r="E47" s="223"/>
+      <c r="F47" s="223"/>
+      <c r="G47" s="223"/>
+      <c r="H47" s="223"/>
+      <c r="I47" s="223"/>
     </row>
     <row r="48" spans="1:9" ht="30">
       <c r="A48" s="41" t="s">
@@ -30167,11 +30273,11 @@
       </c>
       <c r="C48" s="112"/>
       <c r="D48" s="112"/>
-      <c r="E48" s="220"/>
-      <c r="F48" s="220"/>
-      <c r="G48" s="220"/>
-      <c r="H48" s="220"/>
-      <c r="I48" s="220"/>
+      <c r="E48" s="223"/>
+      <c r="F48" s="223"/>
+      <c r="G48" s="223"/>
+      <c r="H48" s="223"/>
+      <c r="I48" s="223"/>
     </row>
     <row r="49" spans="1:9" ht="30">
       <c r="A49" s="41" t="s">
@@ -30182,22 +30288,22 @@
       </c>
       <c r="C49" s="112"/>
       <c r="D49" s="112"/>
-      <c r="E49" s="220"/>
-      <c r="F49" s="220"/>
-      <c r="G49" s="220"/>
-      <c r="H49" s="220"/>
-      <c r="I49" s="220"/>
+      <c r="E49" s="223"/>
+      <c r="F49" s="223"/>
+      <c r="G49" s="223"/>
+      <c r="H49" s="223"/>
+      <c r="I49" s="223"/>
     </row>
     <row r="50" spans="1:9" s="65" customFormat="1">
       <c r="A50" s="41"/>
       <c r="B50" s="112"/>
       <c r="C50" s="112"/>
       <c r="D50" s="112"/>
-      <c r="E50" s="220"/>
-      <c r="F50" s="220"/>
-      <c r="G50" s="220"/>
-      <c r="H50" s="220"/>
-      <c r="I50" s="220"/>
+      <c r="E50" s="223"/>
+      <c r="F50" s="223"/>
+      <c r="G50" s="223"/>
+      <c r="H50" s="223"/>
+      <c r="I50" s="223"/>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" s="111" t="s">
@@ -30208,11 +30314,11 @@
       </c>
       <c r="C51" s="112"/>
       <c r="D51" s="112"/>
-      <c r="E51" s="220"/>
-      <c r="F51" s="220"/>
-      <c r="G51" s="220"/>
-      <c r="H51" s="220"/>
-      <c r="I51" s="220"/>
+      <c r="E51" s="223"/>
+      <c r="F51" s="223"/>
+      <c r="G51" s="223"/>
+      <c r="H51" s="223"/>
+      <c r="I51" s="223"/>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" s="112"/>
@@ -30221,11 +30327,11 @@
       </c>
       <c r="C52" s="112"/>
       <c r="D52" s="112"/>
-      <c r="E52" s="220"/>
-      <c r="F52" s="220"/>
-      <c r="G52" s="220"/>
-      <c r="H52" s="220"/>
-      <c r="I52" s="220"/>
+      <c r="E52" s="223"/>
+      <c r="F52" s="223"/>
+      <c r="G52" s="223"/>
+      <c r="H52" s="223"/>
+      <c r="I52" s="223"/>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" s="112"/>
@@ -30234,11 +30340,11 @@
       </c>
       <c r="C53" s="112"/>
       <c r="D53" s="112"/>
-      <c r="E53" s="220"/>
-      <c r="F53" s="220"/>
-      <c r="G53" s="220"/>
-      <c r="H53" s="220"/>
-      <c r="I53" s="220"/>
+      <c r="E53" s="223"/>
+      <c r="F53" s="223"/>
+      <c r="G53" s="223"/>
+      <c r="H53" s="223"/>
+      <c r="I53" s="223"/>
     </row>
     <row r="54" spans="1:9" ht="30">
       <c r="A54" s="111" t="s">
@@ -30247,11 +30353,11 @@
       <c r="B54" s="112"/>
       <c r="C54" s="112"/>
       <c r="D54" s="112"/>
-      <c r="E54" s="220"/>
-      <c r="F54" s="220"/>
-      <c r="G54" s="220"/>
-      <c r="H54" s="220"/>
-      <c r="I54" s="220"/>
+      <c r="E54" s="223"/>
+      <c r="F54" s="223"/>
+      <c r="G54" s="223"/>
+      <c r="H54" s="223"/>
+      <c r="I54" s="223"/>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="112" t="s">
@@ -30262,11 +30368,11 @@
       </c>
       <c r="C55" s="112"/>
       <c r="D55" s="112"/>
-      <c r="E55" s="220"/>
-      <c r="F55" s="220"/>
-      <c r="G55" s="220"/>
-      <c r="H55" s="220"/>
-      <c r="I55" s="220"/>
+      <c r="E55" s="223"/>
+      <c r="F55" s="223"/>
+      <c r="G55" s="223"/>
+      <c r="H55" s="223"/>
+      <c r="I55" s="223"/>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" s="112"/>
@@ -30275,11 +30381,11 @@
       </c>
       <c r="C56" s="112"/>
       <c r="D56" s="112"/>
-      <c r="E56" s="220"/>
-      <c r="F56" s="220"/>
-      <c r="G56" s="220"/>
-      <c r="H56" s="220"/>
-      <c r="I56" s="220"/>
+      <c r="E56" s="223"/>
+      <c r="F56" s="223"/>
+      <c r="G56" s="223"/>
+      <c r="H56" s="223"/>
+      <c r="I56" s="223"/>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="112" t="s">
@@ -30290,11 +30396,11 @@
       </c>
       <c r="C57" s="112"/>
       <c r="D57" s="112"/>
-      <c r="E57" s="220"/>
-      <c r="F57" s="220"/>
-      <c r="G57" s="220"/>
-      <c r="H57" s="220"/>
-      <c r="I57" s="220"/>
+      <c r="E57" s="223"/>
+      <c r="F57" s="223"/>
+      <c r="G57" s="223"/>
+      <c r="H57" s="223"/>
+      <c r="I57" s="223"/>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="112" t="s">
@@ -30305,11 +30411,11 @@
       </c>
       <c r="C58" s="112"/>
       <c r="D58" s="112"/>
-      <c r="E58" s="220"/>
-      <c r="F58" s="220"/>
-      <c r="G58" s="220"/>
-      <c r="H58" s="220"/>
-      <c r="I58" s="220"/>
+      <c r="E58" s="223"/>
+      <c r="F58" s="223"/>
+      <c r="G58" s="223"/>
+      <c r="H58" s="223"/>
+      <c r="I58" s="223"/>
     </row>
     <row r="59" spans="1:9" ht="60">
       <c r="A59" s="112"/>
@@ -30318,35 +30424,35 @@
       </c>
       <c r="C59" s="112"/>
       <c r="D59" s="112"/>
-      <c r="E59" s="220"/>
-      <c r="F59" s="220"/>
-      <c r="G59" s="220"/>
-      <c r="H59" s="220"/>
-      <c r="I59" s="220"/>
+      <c r="E59" s="223"/>
+      <c r="F59" s="223"/>
+      <c r="G59" s="223"/>
+      <c r="H59" s="223"/>
+      <c r="I59" s="223"/>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" s="112"/>
       <c r="B60" s="112"/>
       <c r="C60" s="112"/>
       <c r="D60" s="112"/>
-      <c r="E60" s="220"/>
-      <c r="F60" s="220"/>
-      <c r="G60" s="220"/>
-      <c r="H60" s="220"/>
-      <c r="I60" s="220"/>
+      <c r="E60" s="223"/>
+      <c r="F60" s="223"/>
+      <c r="G60" s="223"/>
+      <c r="H60" s="223"/>
+      <c r="I60" s="223"/>
     </row>
     <row r="61" spans="1:9">
-      <c r="A61" s="217" t="s">
+      <c r="A61" s="220" t="s">
         <v>3746</v>
       </c>
-      <c r="B61" s="217"/>
-      <c r="C61" s="217"/>
+      <c r="B61" s="220"/>
+      <c r="C61" s="220"/>
       <c r="D61" s="112"/>
-      <c r="E61" s="220"/>
-      <c r="F61" s="220"/>
-      <c r="G61" s="220"/>
-      <c r="H61" s="220"/>
-      <c r="I61" s="220"/>
+      <c r="E61" s="223"/>
+      <c r="F61" s="223"/>
+      <c r="G61" s="223"/>
+      <c r="H61" s="223"/>
+      <c r="I61" s="223"/>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" s="112"/>
@@ -30355,11 +30461,11 @@
       </c>
       <c r="C62" s="112"/>
       <c r="D62" s="112"/>
-      <c r="E62" s="220"/>
-      <c r="F62" s="220"/>
-      <c r="G62" s="220"/>
-      <c r="H62" s="220"/>
-      <c r="I62" s="220"/>
+      <c r="E62" s="223"/>
+      <c r="F62" s="223"/>
+      <c r="G62" s="223"/>
+      <c r="H62" s="223"/>
+      <c r="I62" s="223"/>
     </row>
     <row r="63" spans="1:9" ht="30">
       <c r="A63" s="112"/>
@@ -30368,11 +30474,11 @@
       </c>
       <c r="C63" s="112"/>
       <c r="D63" s="112"/>
-      <c r="E63" s="220"/>
-      <c r="F63" s="220"/>
-      <c r="G63" s="220"/>
-      <c r="H63" s="220"/>
-      <c r="I63" s="220"/>
+      <c r="E63" s="223"/>
+      <c r="F63" s="223"/>
+      <c r="G63" s="223"/>
+      <c r="H63" s="223"/>
+      <c r="I63" s="223"/>
     </row>
     <row r="64" spans="1:9" ht="90">
       <c r="A64" s="112" t="s">
@@ -30383,11 +30489,11 @@
       </c>
       <c r="C64" s="112"/>
       <c r="D64" s="112"/>
-      <c r="E64" s="220"/>
-      <c r="F64" s="220"/>
-      <c r="G64" s="220"/>
-      <c r="H64" s="220"/>
-      <c r="I64" s="220"/>
+      <c r="E64" s="223"/>
+      <c r="F64" s="223"/>
+      <c r="G64" s="223"/>
+      <c r="H64" s="223"/>
+      <c r="I64" s="223"/>
     </row>
     <row r="65" spans="1:9" ht="30">
       <c r="A65" s="23" t="s">
@@ -30398,11 +30504,11 @@
       </c>
       <c r="C65" s="112"/>
       <c r="D65" s="112"/>
-      <c r="E65" s="220"/>
-      <c r="F65" s="220"/>
-      <c r="G65" s="220"/>
-      <c r="H65" s="220"/>
-      <c r="I65" s="220"/>
+      <c r="E65" s="223"/>
+      <c r="F65" s="223"/>
+      <c r="G65" s="223"/>
+      <c r="H65" s="223"/>
+      <c r="I65" s="223"/>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" s="23" t="s">
@@ -30413,11 +30519,11 @@
       </c>
       <c r="C66" s="112"/>
       <c r="D66" s="112"/>
-      <c r="E66" s="220"/>
-      <c r="F66" s="220"/>
-      <c r="G66" s="220"/>
-      <c r="H66" s="220"/>
-      <c r="I66" s="220"/>
+      <c r="E66" s="223"/>
+      <c r="F66" s="223"/>
+      <c r="G66" s="223"/>
+      <c r="H66" s="223"/>
+      <c r="I66" s="223"/>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" s="112" t="s">
@@ -30428,11 +30534,11 @@
       </c>
       <c r="C67" s="112"/>
       <c r="D67" s="112"/>
-      <c r="E67" s="220"/>
-      <c r="F67" s="220"/>
-      <c r="G67" s="220"/>
-      <c r="H67" s="220"/>
-      <c r="I67" s="220"/>
+      <c r="E67" s="223"/>
+      <c r="F67" s="223"/>
+      <c r="G67" s="223"/>
+      <c r="H67" s="223"/>
+      <c r="I67" s="223"/>
     </row>
     <row r="68" spans="1:9" s="67" customFormat="1">
       <c r="A68" s="112" t="s">
@@ -30443,11 +30549,11 @@
       </c>
       <c r="C68" s="112"/>
       <c r="D68" s="112"/>
-      <c r="E68" s="220"/>
-      <c r="F68" s="220"/>
-      <c r="G68" s="220"/>
-      <c r="H68" s="220"/>
-      <c r="I68" s="220"/>
+      <c r="E68" s="223"/>
+      <c r="F68" s="223"/>
+      <c r="G68" s="223"/>
+      <c r="H68" s="223"/>
+      <c r="I68" s="223"/>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" s="112" t="s">
@@ -30458,11 +30564,11 @@
       </c>
       <c r="C69" s="112"/>
       <c r="D69" s="112"/>
-      <c r="E69" s="220"/>
-      <c r="F69" s="220"/>
-      <c r="G69" s="220"/>
-      <c r="H69" s="220"/>
-      <c r="I69" s="220"/>
+      <c r="E69" s="223"/>
+      <c r="F69" s="223"/>
+      <c r="G69" s="223"/>
+      <c r="H69" s="223"/>
+      <c r="I69" s="223"/>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" s="112" t="s">
@@ -30473,11 +30579,11 @@
       </c>
       <c r="C70" s="112"/>
       <c r="D70" s="112"/>
-      <c r="E70" s="220"/>
-      <c r="F70" s="220"/>
-      <c r="G70" s="220"/>
-      <c r="H70" s="220"/>
-      <c r="I70" s="220"/>
+      <c r="E70" s="223"/>
+      <c r="F70" s="223"/>
+      <c r="G70" s="223"/>
+      <c r="H70" s="223"/>
+      <c r="I70" s="223"/>
     </row>
     <row r="71" spans="1:9" ht="30">
       <c r="A71" s="112" t="s">
@@ -30488,11 +30594,11 @@
       </c>
       <c r="C71" s="112"/>
       <c r="D71" s="112"/>
-      <c r="E71" s="220"/>
-      <c r="F71" s="220"/>
-      <c r="G71" s="220"/>
-      <c r="H71" s="220"/>
-      <c r="I71" s="220"/>
+      <c r="E71" s="223"/>
+      <c r="F71" s="223"/>
+      <c r="G71" s="223"/>
+      <c r="H71" s="223"/>
+      <c r="I71" s="223"/>
     </row>
     <row r="72" spans="1:9" ht="30">
       <c r="A72" s="112" t="s">
@@ -30503,11 +30609,11 @@
       </c>
       <c r="C72" s="112"/>
       <c r="D72" s="112"/>
-      <c r="E72" s="220"/>
-      <c r="F72" s="220"/>
-      <c r="G72" s="220"/>
-      <c r="H72" s="220"/>
-      <c r="I72" s="220"/>
+      <c r="E72" s="223"/>
+      <c r="F72" s="223"/>
+      <c r="G72" s="223"/>
+      <c r="H72" s="223"/>
+      <c r="I72" s="223"/>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" s="23" t="s">
@@ -30518,11 +30624,11 @@
       </c>
       <c r="C73" s="112"/>
       <c r="D73" s="112"/>
-      <c r="E73" s="220"/>
-      <c r="F73" s="220"/>
-      <c r="G73" s="220"/>
-      <c r="H73" s="220"/>
-      <c r="I73" s="220"/>
+      <c r="E73" s="223"/>
+      <c r="F73" s="223"/>
+      <c r="G73" s="223"/>
+      <c r="H73" s="223"/>
+      <c r="I73" s="223"/>
     </row>
     <row r="74" spans="1:9" s="68" customFormat="1" ht="30">
       <c r="A74" s="23" t="s">
@@ -30533,11 +30639,11 @@
       </c>
       <c r="C74" s="112"/>
       <c r="D74" s="112"/>
-      <c r="E74" s="220"/>
-      <c r="F74" s="220"/>
-      <c r="G74" s="220"/>
-      <c r="H74" s="220"/>
-      <c r="I74" s="220"/>
+      <c r="E74" s="223"/>
+      <c r="F74" s="223"/>
+      <c r="G74" s="223"/>
+      <c r="H74" s="223"/>
+      <c r="I74" s="223"/>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" s="23" t="s">
@@ -30548,11 +30654,11 @@
       </c>
       <c r="C75" s="112"/>
       <c r="D75" s="112"/>
-      <c r="E75" s="220"/>
-      <c r="F75" s="220"/>
-      <c r="G75" s="220"/>
-      <c r="H75" s="220"/>
-      <c r="I75" s="220"/>
+      <c r="E75" s="223"/>
+      <c r="F75" s="223"/>
+      <c r="G75" s="223"/>
+      <c r="H75" s="223"/>
+      <c r="I75" s="223"/>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" s="23" t="s">
@@ -30563,46 +30669,46 @@
       </c>
       <c r="C76" s="112"/>
       <c r="D76" s="112"/>
-      <c r="E76" s="220"/>
-      <c r="F76" s="220"/>
-      <c r="G76" s="220"/>
-      <c r="H76" s="220"/>
-      <c r="I76" s="220"/>
+      <c r="E76" s="223"/>
+      <c r="F76" s="223"/>
+      <c r="G76" s="223"/>
+      <c r="H76" s="223"/>
+      <c r="I76" s="223"/>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" s="112"/>
       <c r="B77" s="112"/>
       <c r="C77" s="112"/>
       <c r="D77" s="112"/>
-      <c r="E77" s="220"/>
-      <c r="F77" s="220"/>
-      <c r="G77" s="220"/>
-      <c r="H77" s="220"/>
-      <c r="I77" s="220"/>
+      <c r="E77" s="223"/>
+      <c r="F77" s="223"/>
+      <c r="G77" s="223"/>
+      <c r="H77" s="223"/>
+      <c r="I77" s="223"/>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" s="23"/>
       <c r="B78" s="112"/>
       <c r="C78" s="112"/>
       <c r="D78" s="112"/>
-      <c r="E78" s="220"/>
-      <c r="F78" s="220"/>
-      <c r="G78" s="220"/>
-      <c r="H78" s="220"/>
-      <c r="I78" s="220"/>
+      <c r="E78" s="223"/>
+      <c r="F78" s="223"/>
+      <c r="G78" s="223"/>
+      <c r="H78" s="223"/>
+      <c r="I78" s="223"/>
     </row>
     <row r="79" spans="1:9">
-      <c r="A79" s="222" t="s">
+      <c r="A79" s="225" t="s">
         <v>3770</v>
       </c>
-      <c r="B79" s="222"/>
-      <c r="C79" s="222"/>
+      <c r="B79" s="225"/>
+      <c r="C79" s="225"/>
       <c r="D79" s="112"/>
-      <c r="E79" s="220"/>
-      <c r="F79" s="220"/>
-      <c r="G79" s="220"/>
-      <c r="H79" s="220"/>
-      <c r="I79" s="220"/>
+      <c r="E79" s="223"/>
+      <c r="F79" s="223"/>
+      <c r="G79" s="223"/>
+      <c r="H79" s="223"/>
+      <c r="I79" s="223"/>
     </row>
     <row r="80" spans="1:9" ht="30">
       <c r="A80" s="112"/>
@@ -30611,22 +30717,22 @@
       </c>
       <c r="C80" s="112"/>
       <c r="D80" s="112"/>
-      <c r="E80" s="220"/>
-      <c r="F80" s="220"/>
-      <c r="G80" s="220"/>
-      <c r="H80" s="220"/>
-      <c r="I80" s="220"/>
+      <c r="E80" s="223"/>
+      <c r="F80" s="223"/>
+      <c r="G80" s="223"/>
+      <c r="H80" s="223"/>
+      <c r="I80" s="223"/>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" s="112"/>
       <c r="B81" s="112"/>
       <c r="C81" s="112"/>
       <c r="D81" s="112"/>
-      <c r="E81" s="220"/>
-      <c r="F81" s="220"/>
-      <c r="G81" s="220"/>
-      <c r="H81" s="220"/>
-      <c r="I81" s="220"/>
+      <c r="E81" s="223"/>
+      <c r="F81" s="223"/>
+      <c r="G81" s="223"/>
+      <c r="H81" s="223"/>
+      <c r="I81" s="223"/>
     </row>
     <row r="82" spans="1:9" ht="30">
       <c r="A82" s="111" t="s">
@@ -30637,11 +30743,11 @@
       </c>
       <c r="C82" s="112"/>
       <c r="D82" s="112"/>
-      <c r="E82" s="220"/>
-      <c r="F82" s="220"/>
-      <c r="G82" s="220"/>
-      <c r="H82" s="220"/>
-      <c r="I82" s="220"/>
+      <c r="E82" s="223"/>
+      <c r="F82" s="223"/>
+      <c r="G82" s="223"/>
+      <c r="H82" s="223"/>
+      <c r="I82" s="223"/>
     </row>
     <row r="83" spans="1:9" ht="30">
       <c r="A83" s="23" t="s">
@@ -30652,11 +30758,11 @@
       </c>
       <c r="C83" s="112"/>
       <c r="D83" s="112"/>
-      <c r="E83" s="220"/>
-      <c r="F83" s="220"/>
-      <c r="G83" s="220"/>
-      <c r="H83" s="220"/>
-      <c r="I83" s="220"/>
+      <c r="E83" s="223"/>
+      <c r="F83" s="223"/>
+      <c r="G83" s="223"/>
+      <c r="H83" s="223"/>
+      <c r="I83" s="223"/>
     </row>
     <row r="84" spans="1:9" ht="30">
       <c r="A84" s="112" t="s">
@@ -30667,11 +30773,11 @@
       </c>
       <c r="C84" s="112"/>
       <c r="D84" s="112"/>
-      <c r="E84" s="220"/>
-      <c r="F84" s="220"/>
-      <c r="G84" s="220"/>
-      <c r="H84" s="220"/>
-      <c r="I84" s="220"/>
+      <c r="E84" s="223"/>
+      <c r="F84" s="223"/>
+      <c r="G84" s="223"/>
+      <c r="H84" s="223"/>
+      <c r="I84" s="223"/>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" s="112" t="s">
@@ -30682,11 +30788,11 @@
       </c>
       <c r="C85" s="112"/>
       <c r="D85" s="112"/>
-      <c r="E85" s="220"/>
-      <c r="F85" s="220"/>
-      <c r="G85" s="220"/>
-      <c r="H85" s="220"/>
-      <c r="I85" s="220"/>
+      <c r="E85" s="223"/>
+      <c r="F85" s="223"/>
+      <c r="G85" s="223"/>
+      <c r="H85" s="223"/>
+      <c r="I85" s="223"/>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" s="112" t="s">
@@ -30697,11 +30803,11 @@
       </c>
       <c r="C86" s="112"/>
       <c r="D86" s="112"/>
-      <c r="E86" s="220"/>
-      <c r="F86" s="220"/>
-      <c r="G86" s="220"/>
-      <c r="H86" s="220"/>
-      <c r="I86" s="220"/>
+      <c r="E86" s="223"/>
+      <c r="F86" s="223"/>
+      <c r="G86" s="223"/>
+      <c r="H86" s="223"/>
+      <c r="I86" s="223"/>
     </row>
     <row r="87" spans="1:9" ht="60">
       <c r="A87" s="112" t="s">
@@ -30712,11 +30818,11 @@
       </c>
       <c r="C87" s="112"/>
       <c r="D87" s="112"/>
-      <c r="E87" s="220"/>
-      <c r="F87" s="220"/>
-      <c r="G87" s="220"/>
-      <c r="H87" s="220"/>
-      <c r="I87" s="220"/>
+      <c r="E87" s="223"/>
+      <c r="F87" s="223"/>
+      <c r="G87" s="223"/>
+      <c r="H87" s="223"/>
+      <c r="I87" s="223"/>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" s="111" t="s">
@@ -30725,11 +30831,11 @@
       <c r="B88" s="112"/>
       <c r="C88" s="112"/>
       <c r="D88" s="112"/>
-      <c r="E88" s="220"/>
-      <c r="F88" s="220"/>
-      <c r="G88" s="220"/>
-      <c r="H88" s="220"/>
-      <c r="I88" s="220"/>
+      <c r="E88" s="223"/>
+      <c r="F88" s="223"/>
+      <c r="G88" s="223"/>
+      <c r="H88" s="223"/>
+      <c r="I88" s="223"/>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" s="112" t="s">
@@ -30740,11 +30846,11 @@
       </c>
       <c r="C89" s="112"/>
       <c r="D89" s="112"/>
-      <c r="E89" s="220"/>
-      <c r="F89" s="220"/>
-      <c r="G89" s="220"/>
-      <c r="H89" s="220"/>
-      <c r="I89" s="220"/>
+      <c r="E89" s="223"/>
+      <c r="F89" s="223"/>
+      <c r="G89" s="223"/>
+      <c r="H89" s="223"/>
+      <c r="I89" s="223"/>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" s="112" t="s">
@@ -30755,11 +30861,11 @@
       </c>
       <c r="C90" s="112"/>
       <c r="D90" s="112"/>
-      <c r="E90" s="220"/>
-      <c r="F90" s="220"/>
-      <c r="G90" s="220"/>
-      <c r="H90" s="220"/>
-      <c r="I90" s="220"/>
+      <c r="E90" s="223"/>
+      <c r="F90" s="223"/>
+      <c r="G90" s="223"/>
+      <c r="H90" s="223"/>
+      <c r="I90" s="223"/>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" s="112" t="s">
@@ -30770,11 +30876,11 @@
       </c>
       <c r="C91" s="112"/>
       <c r="D91" s="112"/>
-      <c r="E91" s="220"/>
-      <c r="F91" s="220"/>
-      <c r="G91" s="220"/>
-      <c r="H91" s="220"/>
-      <c r="I91" s="220"/>
+      <c r="E91" s="223"/>
+      <c r="F91" s="223"/>
+      <c r="G91" s="223"/>
+      <c r="H91" s="223"/>
+      <c r="I91" s="223"/>
     </row>
     <row r="92" spans="1:9" ht="45">
       <c r="A92" s="112" t="s">
@@ -30792,11 +30898,11 @@
       <c r="I92" s="112"/>
     </row>
     <row r="94" spans="1:9">
-      <c r="A94" s="188" t="s">
+      <c r="A94" s="191" t="s">
         <v>3790</v>
       </c>
-      <c r="B94" s="188"/>
-      <c r="C94" s="188"/>
+      <c r="B94" s="191"/>
+      <c r="C94" s="191"/>
       <c r="D94" s="112"/>
       <c r="E94" s="112"/>
       <c r="F94" s="112"/>
@@ -31347,11 +31453,11 @@
       <c r="C1" s="178"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="188" t="s">
+      <c r="A3" s="191" t="s">
         <v>4507</v>
       </c>
-      <c r="B3" s="188"/>
-      <c r="C3" s="188"/>
+      <c r="B3" s="191"/>
+      <c r="C3" s="191"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="177" t="s">
@@ -31362,11 +31468,11 @@
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="188" t="s">
+      <c r="A6" s="191" t="s">
         <v>4510</v>
       </c>
-      <c r="B6" s="188"/>
-      <c r="C6" s="188"/>
+      <c r="B6" s="191"/>
+      <c r="C6" s="191"/>
     </row>
     <row r="8" spans="1:3">
       <c r="B8" s="177" t="s">
@@ -31394,11 +31500,11 @@
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="189" t="s">
+      <c r="A17" s="192" t="s">
         <v>4503</v>
       </c>
-      <c r="B17" s="189"/>
-      <c r="C17" s="189"/>
+      <c r="B17" s="192"/>
+      <c r="C17" s="192"/>
     </row>
     <row r="18" spans="1:3" ht="45">
       <c r="A18" s="179"/>
@@ -31436,7 +31542,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D92C6C6-D4A0-4FAE-85D4-2B5F32E0E3B9}">
-  <dimension ref="A1:C254"/>
+  <dimension ref="A1:C286"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="44.140625" style="163" customWidth="1"/>
@@ -31454,11 +31560,11 @@
       <c r="C1" s="161"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="189" t="s">
+      <c r="A3" s="192" t="s">
         <v>3886</v>
       </c>
-      <c r="B3" s="189"/>
-      <c r="C3" s="189"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="192"/>
     </row>
     <row r="4" spans="1:3" ht="45">
       <c r="A4" s="162"/>
@@ -31493,14 +31599,14 @@
     <row r="8" spans="1:3">
       <c r="A8" s="162"/>
       <c r="B8" s="162"/>
-      <c r="C8" s="191"/>
+      <c r="C8" s="194"/>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="164" t="s">
         <v>3890</v>
       </c>
       <c r="B9" s="162"/>
-      <c r="C9" s="191"/>
+      <c r="C9" s="194"/>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="162" t="s">
@@ -31509,7 +31615,7 @@
       <c r="B10" s="162" t="s">
         <v>3903</v>
       </c>
-      <c r="C10" s="191"/>
+      <c r="C10" s="194"/>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="162" t="s">
@@ -31518,7 +31624,7 @@
       <c r="B11" s="162" t="s">
         <v>3902</v>
       </c>
-      <c r="C11" s="191"/>
+      <c r="C11" s="194"/>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="162" t="s">
@@ -31527,7 +31633,7 @@
       <c r="B12" s="162" t="s">
         <v>3899</v>
       </c>
-      <c r="C12" s="191"/>
+      <c r="C12" s="194"/>
     </row>
     <row r="13" spans="1:3" ht="30">
       <c r="A13" s="162" t="s">
@@ -31536,7 +31642,7 @@
       <c r="B13" s="162" t="s">
         <v>3896</v>
       </c>
-      <c r="C13" s="191"/>
+      <c r="C13" s="194"/>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="162" t="s">
@@ -31545,7 +31651,7 @@
       <c r="B14" s="162" t="s">
         <v>3900</v>
       </c>
-      <c r="C14" s="191"/>
+      <c r="C14" s="194"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="162" t="s">
@@ -31554,7 +31660,7 @@
       <c r="B15" s="162" t="s">
         <v>3901</v>
       </c>
-      <c r="C15" s="191"/>
+      <c r="C15" s="194"/>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="162" t="s">
@@ -31563,7 +31669,7 @@
       <c r="B16" s="162" t="s">
         <v>3898</v>
       </c>
-      <c r="C16" s="191"/>
+      <c r="C16" s="194"/>
     </row>
     <row r="17" spans="1:3" ht="30">
       <c r="A17" s="162" t="s">
@@ -31572,7 +31678,7 @@
       <c r="B17" s="162" t="s">
         <v>3905</v>
       </c>
-      <c r="C17" s="191"/>
+      <c r="C17" s="194"/>
     </row>
     <row r="18" spans="1:3" ht="30">
       <c r="A18" s="162" t="s">
@@ -31581,7 +31687,7 @@
       <c r="B18" s="162" t="s">
         <v>3949</v>
       </c>
-      <c r="C18" s="191"/>
+      <c r="C18" s="194"/>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="162" t="s">
@@ -31590,7 +31696,7 @@
       <c r="B19" s="162" t="s">
         <v>3951</v>
       </c>
-      <c r="C19" s="191"/>
+      <c r="C19" s="194"/>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="162" t="s">
@@ -31599,14 +31705,14 @@
       <c r="B20" s="162" t="s">
         <v>3953</v>
       </c>
-      <c r="C20" s="191"/>
+      <c r="C20" s="194"/>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="164" t="s">
         <v>3906</v>
       </c>
       <c r="B21" s="162"/>
-      <c r="C21" s="191"/>
+      <c r="C21" s="194"/>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="162" t="s">
@@ -31615,7 +31721,7 @@
       <c r="B22" s="162" t="s">
         <v>3909</v>
       </c>
-      <c r="C22" s="191"/>
+      <c r="C22" s="194"/>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="162" t="s">
@@ -31624,7 +31730,7 @@
       <c r="B23" s="162" t="s">
         <v>3908</v>
       </c>
-      <c r="C23" s="191"/>
+      <c r="C23" s="194"/>
     </row>
     <row r="24" spans="1:3" ht="30">
       <c r="A24" s="162" t="s">
@@ -31633,7 +31739,7 @@
       <c r="B24" s="162" t="s">
         <v>3910</v>
       </c>
-      <c r="C24" s="191"/>
+      <c r="C24" s="194"/>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="162" t="s">
@@ -31642,7 +31748,7 @@
       <c r="B25" s="162" t="s">
         <v>3900</v>
       </c>
-      <c r="C25" s="191"/>
+      <c r="C25" s="194"/>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="162" t="s">
@@ -31651,7 +31757,7 @@
       <c r="B26" s="162" t="s">
         <v>3901</v>
       </c>
-      <c r="C26" s="191"/>
+      <c r="C26" s="194"/>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="162" t="s">
@@ -31660,7 +31766,7 @@
       <c r="B27" s="162" t="s">
         <v>3898</v>
       </c>
-      <c r="C27" s="191"/>
+      <c r="C27" s="194"/>
     </row>
     <row r="28" spans="1:3" ht="30">
       <c r="A28" s="162" t="s">
@@ -32136,11 +32242,11 @@
       <c r="C82" s="162"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="189" t="s">
+      <c r="A83" s="192" t="s">
         <v>3990</v>
       </c>
-      <c r="B83" s="189"/>
-      <c r="C83" s="189"/>
+      <c r="B83" s="192"/>
+      <c r="C83" s="192"/>
     </row>
     <row r="84" spans="1:3">
       <c r="A84" s="162"/>
@@ -32203,11 +32309,11 @@
       <c r="C91" s="162"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="189" t="s">
+      <c r="A92" s="192" t="s">
         <v>4036</v>
       </c>
-      <c r="B92" s="189"/>
-      <c r="C92" s="189"/>
+      <c r="B92" s="192"/>
+      <c r="C92" s="192"/>
     </row>
     <row r="93" spans="1:3" ht="75">
       <c r="A93" s="162"/>
@@ -32292,11 +32398,11 @@
       </c>
     </row>
     <row r="104" spans="1:3">
-      <c r="A104" s="189" t="s">
+      <c r="A104" s="192" t="s">
         <v>4076</v>
       </c>
-      <c r="B104" s="189"/>
-      <c r="C104" s="189"/>
+      <c r="B104" s="192"/>
+      <c r="C104" s="192"/>
     </row>
     <row r="105" spans="1:3" ht="285">
       <c r="B105" s="163" t="s">
@@ -32463,11 +32569,11 @@
       </c>
     </row>
     <row r="128" spans="1:3">
-      <c r="A128" s="189" t="s">
+      <c r="A128" s="192" t="s">
         <v>4150</v>
       </c>
-      <c r="B128" s="189"/>
-      <c r="C128" s="189"/>
+      <c r="B128" s="192"/>
+      <c r="C128" s="192"/>
     </row>
     <row r="129" spans="1:3" ht="105">
       <c r="B129" s="163" t="s">
@@ -32619,11 +32725,11 @@
       </c>
     </row>
     <row r="150" spans="1:3">
-      <c r="A150" s="189" t="s">
+      <c r="A150" s="192" t="s">
         <v>4187</v>
       </c>
-      <c r="B150" s="189"/>
-      <c r="C150" s="189"/>
+      <c r="B150" s="192"/>
+      <c r="C150" s="192"/>
     </row>
     <row r="151" spans="1:3" ht="90">
       <c r="B151" s="163" t="s">
@@ -32631,11 +32737,11 @@
       </c>
     </row>
     <row r="155" spans="1:3">
-      <c r="A155" s="189" t="s">
+      <c r="A155" s="192" t="s">
         <v>4183</v>
       </c>
-      <c r="B155" s="189"/>
-      <c r="C155" s="189"/>
+      <c r="B155" s="192"/>
+      <c r="C155" s="192"/>
     </row>
     <row r="156" spans="1:3" ht="75">
       <c r="B156" s="163" t="s">
@@ -32651,11 +32757,11 @@
       </c>
     </row>
     <row r="158" spans="1:3">
-      <c r="A158" s="188" t="s">
+      <c r="A158" s="191" t="s">
         <v>4241</v>
       </c>
-      <c r="B158" s="188"/>
-      <c r="C158" s="188"/>
+      <c r="B158" s="191"/>
+      <c r="C158" s="191"/>
     </row>
     <row r="159" spans="1:3">
       <c r="A159" s="162"/>
@@ -32746,11 +32852,11 @@
       </c>
     </row>
     <row r="169" spans="1:3">
-      <c r="A169" s="188" t="s">
+      <c r="A169" s="191" t="s">
         <v>4299</v>
       </c>
-      <c r="B169" s="188"/>
-      <c r="C169" s="188"/>
+      <c r="B169" s="191"/>
+      <c r="C169" s="191"/>
     </row>
     <row r="170" spans="1:3" ht="30">
       <c r="B170" s="163" t="s">
@@ -32798,11 +32904,11 @@
       </c>
     </row>
     <row r="183" spans="1:3">
-      <c r="A183" s="189" t="s">
+      <c r="A183" s="192" t="s">
         <v>4329</v>
       </c>
-      <c r="B183" s="189"/>
-      <c r="C183" s="189"/>
+      <c r="B183" s="192"/>
+      <c r="C183" s="192"/>
     </row>
     <row r="184" spans="1:3" ht="45">
       <c r="B184" s="163" t="s">
@@ -32810,11 +32916,11 @@
       </c>
     </row>
     <row r="185" spans="1:3">
-      <c r="A185" s="188" t="s">
+      <c r="A185" s="191" t="s">
         <v>4038</v>
       </c>
-      <c r="B185" s="188"/>
-      <c r="C185" s="188"/>
+      <c r="B185" s="191"/>
+      <c r="C185" s="191"/>
     </row>
     <row r="186" spans="1:3" ht="60">
       <c r="A186" s="163" t="s">
@@ -32844,11 +32950,11 @@
       </c>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189" s="188" t="s">
+      <c r="A189" s="191" t="s">
         <v>1846</v>
       </c>
-      <c r="B189" s="188"/>
-      <c r="C189" s="188"/>
+      <c r="B189" s="191"/>
+      <c r="C189" s="191"/>
     </row>
     <row r="190" spans="1:3">
       <c r="A190" s="162"/>
@@ -32965,11 +33071,11 @@
       </c>
     </row>
     <row r="205" spans="1:3">
-      <c r="A205" s="188" t="s">
+      <c r="A205" s="191" t="s">
         <v>4340</v>
       </c>
-      <c r="B205" s="188"/>
-      <c r="C205" s="188"/>
+      <c r="B205" s="191"/>
+      <c r="C205" s="191"/>
     </row>
     <row r="206" spans="1:3">
       <c r="A206" s="163" t="s">
@@ -33054,235 +33160,378 @@
         <v>3639</v>
       </c>
     </row>
-    <row r="217" spans="1:3">
-      <c r="A217" s="189" t="s">
+    <row r="216" spans="1:3" s="183" customFormat="1">
+      <c r="A216" s="191" t="s">
+        <v>4514</v>
+      </c>
+      <c r="B216" s="191"/>
+      <c r="C216" s="191"/>
+    </row>
+    <row r="217" spans="1:3" s="183" customFormat="1">
+      <c r="B217" s="183" t="s">
+        <v>4515</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" s="183" customFormat="1">
+      <c r="A218" s="185" t="s">
+        <v>4516</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" s="183" customFormat="1" ht="45">
+      <c r="A219" s="76" t="s">
+        <v>4517</v>
+      </c>
+      <c r="B219" s="183" t="s">
+        <v>4527</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" s="183" customFormat="1" ht="30">
+      <c r="A220" s="76" t="s">
+        <v>4518</v>
+      </c>
+      <c r="B220" s="183" t="s">
+        <v>4528</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" s="183" customFormat="1">
+      <c r="A221" s="76" t="s">
+        <v>4519</v>
+      </c>
+      <c r="B221" s="183" t="s">
+        <v>4529</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" s="183" customFormat="1">
+      <c r="A222" s="76" t="s">
+        <v>4520</v>
+      </c>
+      <c r="B222" s="183" t="s">
+        <v>4530</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" s="183" customFormat="1" ht="30">
+      <c r="A223" s="76" t="s">
+        <v>4521</v>
+      </c>
+      <c r="B223" s="183" t="s">
+        <v>4531</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" s="183" customFormat="1">
+      <c r="A224" s="76" t="s">
+        <v>4522</v>
+      </c>
+      <c r="B224" s="183" t="s">
+        <v>4532</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" s="183" customFormat="1">
+      <c r="A225" s="76" t="s">
+        <v>4523</v>
+      </c>
+      <c r="B225" s="183" t="s">
+        <v>4533</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" s="183" customFormat="1">
+      <c r="A226" s="76" t="s">
+        <v>4524</v>
+      </c>
+      <c r="B226" s="183" t="s">
+        <v>4534</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" s="183" customFormat="1">
+      <c r="A227" s="76" t="s">
+        <v>4525</v>
+      </c>
+      <c r="B227" s="183" t="s">
+        <v>4535</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" s="183" customFormat="1">
+      <c r="A228" s="76" t="s">
+        <v>4526</v>
+      </c>
+      <c r="B228" s="183" t="s">
+        <v>4536</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" s="183" customFormat="1">
+      <c r="A229" s="185" t="s">
+        <v>4537</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" s="183" customFormat="1" ht="195">
+      <c r="A230" s="184" t="s">
+        <v>4538</v>
+      </c>
+      <c r="B230" s="183" t="s">
+        <v>4539</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" s="183" customFormat="1">
+      <c r="A231" s="184"/>
+    </row>
+    <row r="232" spans="1:2" s="183" customFormat="1">
+      <c r="A232" s="184"/>
+    </row>
+    <row r="233" spans="1:2" s="183" customFormat="1">
+      <c r="A233" s="184"/>
+    </row>
+    <row r="234" spans="1:2" s="183" customFormat="1">
+      <c r="A234" s="184"/>
+    </row>
+    <row r="235" spans="1:2" s="183" customFormat="1">
+      <c r="A235" s="184"/>
+    </row>
+    <row r="236" spans="1:2" s="183" customFormat="1">
+      <c r="A236" s="184"/>
+    </row>
+    <row r="237" spans="1:2" s="183" customFormat="1">
+      <c r="A237" s="184"/>
+    </row>
+    <row r="238" spans="1:2" s="183" customFormat="1">
+      <c r="A238" s="184"/>
+    </row>
+    <row r="239" spans="1:2" s="183" customFormat="1"/>
+    <row r="240" spans="1:2" s="183" customFormat="1"/>
+    <row r="241" spans="1:3" s="183" customFormat="1"/>
+    <row r="242" spans="1:3" s="183" customFormat="1"/>
+    <row r="243" spans="1:3" s="183" customFormat="1"/>
+    <row r="244" spans="1:3" s="183" customFormat="1"/>
+    <row r="245" spans="1:3" s="183" customFormat="1"/>
+    <row r="246" spans="1:3" s="183" customFormat="1"/>
+    <row r="247" spans="1:3" s="183" customFormat="1"/>
+    <row r="249" spans="1:3">
+      <c r="A249" s="192" t="s">
         <v>4376</v>
       </c>
-      <c r="B217" s="189"/>
-      <c r="C217" s="189"/>
-    </row>
-    <row r="218" spans="1:3" ht="30">
-      <c r="B218" s="163" t="s">
+      <c r="B249" s="192"/>
+      <c r="C249" s="192"/>
+    </row>
+    <row r="250" spans="1:3" ht="30">
+      <c r="B250" s="163" t="s">
         <v>4455</v>
       </c>
     </row>
-    <row r="219" spans="1:3">
-      <c r="A219" s="188" t="s">
+    <row r="251" spans="1:3">
+      <c r="A251" s="191" t="s">
         <v>1846</v>
       </c>
-      <c r="B219" s="188"/>
-      <c r="C219" s="188"/>
-    </row>
-    <row r="220" spans="1:3">
-      <c r="A220" s="163" t="s">
+      <c r="B251" s="191"/>
+      <c r="C251" s="191"/>
+    </row>
+    <row r="252" spans="1:3">
+      <c r="A252" s="163" t="s">
         <v>4377</v>
       </c>
-      <c r="B220" s="163" t="s">
+      <c r="B252" s="163" t="s">
         <v>4378</v>
       </c>
     </row>
-    <row r="221" spans="1:3">
-      <c r="A221" s="163" t="s">
+    <row r="253" spans="1:3">
+      <c r="A253" s="163" t="s">
         <v>4379</v>
       </c>
-      <c r="B221" s="163" t="s">
+      <c r="B253" s="163" t="s">
         <v>4380</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="285">
-      <c r="A222" s="163" t="s">
+    <row r="254" spans="1:3" ht="285">
+      <c r="A254" s="163" t="s">
         <v>4381</v>
       </c>
-      <c r="B222" s="163" t="s">
+      <c r="B254" s="163" t="s">
         <v>4382</v>
       </c>
-      <c r="C222" s="163" t="s">
+      <c r="C254" s="163" t="s">
         <v>4383</v>
       </c>
     </row>
-    <row r="223" spans="1:3">
-      <c r="A223" s="165" t="s">
+    <row r="255" spans="1:3">
+      <c r="A255" s="165" t="s">
         <v>1179</v>
       </c>
     </row>
-    <row r="224" spans="1:3">
-      <c r="A224" s="41" t="s">
+    <row r="256" spans="1:3">
+      <c r="A256" s="41" t="s">
         <v>4384</v>
       </c>
-      <c r="B224" s="166" t="s">
+      <c r="B256" s="166" t="s">
         <v>4385</v>
       </c>
-      <c r="C224" s="163" t="s">
+      <c r="C256" s="163" t="s">
         <v>4386</v>
       </c>
     </row>
-    <row r="228" spans="1:3">
-      <c r="B228" s="23"/>
-    </row>
-    <row r="230" spans="1:3">
-      <c r="A230" s="165" t="s">
+    <row r="260" spans="1:3">
+      <c r="B260" s="23"/>
+    </row>
+    <row r="262" spans="1:3">
+      <c r="A262" s="165" t="s">
         <v>4387</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="105">
-      <c r="A231" s="163" t="s">
+    <row r="263" spans="1:3" ht="105">
+      <c r="A263" s="163" t="s">
         <v>4388</v>
       </c>
-      <c r="B231" s="163" t="s">
+      <c r="B263" s="163" t="s">
         <v>4389</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="90">
-      <c r="A232" s="163" t="s">
+    <row r="264" spans="1:3" ht="90">
+      <c r="A264" s="163" t="s">
         <v>4390</v>
       </c>
-      <c r="B232" s="163" t="s">
+      <c r="B264" s="163" t="s">
         <v>4391</v>
       </c>
     </row>
-    <row r="233" spans="1:3">
-      <c r="A233" s="173" t="s">
+    <row r="265" spans="1:3">
+      <c r="A265" s="173" t="s">
         <v>4456</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="150">
-      <c r="A234" s="163" t="s">
+    <row r="266" spans="1:3" ht="150">
+      <c r="A266" s="163" t="s">
         <v>4457</v>
       </c>
-      <c r="B234" s="163" t="s">
+      <c r="B266" s="163" t="s">
         <v>4458</v>
       </c>
     </row>
-    <row r="235" spans="1:3">
-      <c r="B235" s="163" t="s">
+    <row r="267" spans="1:3">
+      <c r="B267" s="163" t="s">
         <v>4112</v>
       </c>
     </row>
-    <row r="236" spans="1:3">
-      <c r="A236" s="189" t="s">
+    <row r="268" spans="1:3">
+      <c r="A268" s="192" t="s">
         <v>4474</v>
       </c>
-      <c r="B236" s="189"/>
-      <c r="C236" s="189"/>
-    </row>
-    <row r="237" spans="1:3" ht="90">
-      <c r="B237" s="163" t="s">
+      <c r="B268" s="192"/>
+      <c r="C268" s="192"/>
+    </row>
+    <row r="269" spans="1:3" ht="90">
+      <c r="B269" s="163" t="s">
         <v>4475</v>
       </c>
     </row>
-    <row r="238" spans="1:3">
-      <c r="A238" s="176" t="s">
+    <row r="270" spans="1:3">
+      <c r="A270" s="176" t="s">
         <v>4476</v>
       </c>
     </row>
-    <row r="239" spans="1:3">
-      <c r="A239" s="163" t="s">
+    <row r="271" spans="1:3">
+      <c r="A271" s="163" t="s">
         <v>4477</v>
       </c>
-      <c r="B239" s="163" t="s">
+      <c r="B271" s="163" t="s">
         <v>4480</v>
       </c>
-      <c r="C239" s="190" t="s">
+      <c r="C271" s="193" t="s">
         <v>4483</v>
       </c>
     </row>
-    <row r="240" spans="1:3">
-      <c r="A240" s="163" t="s">
+    <row r="272" spans="1:3">
+      <c r="A272" s="163" t="s">
         <v>4478</v>
       </c>
-      <c r="B240" s="163" t="s">
+      <c r="B272" s="163" t="s">
         <v>4481</v>
       </c>
-      <c r="C240" s="190"/>
-    </row>
-    <row r="241" spans="1:3">
-      <c r="A241" s="163" t="s">
+      <c r="C272" s="193"/>
+    </row>
+    <row r="273" spans="1:3">
+      <c r="A273" s="163" t="s">
         <v>4479</v>
       </c>
-      <c r="B241" s="163" t="s">
+      <c r="B273" s="163" t="s">
         <v>4482</v>
       </c>
-      <c r="C241" s="190"/>
-    </row>
-    <row r="242" spans="1:3">
-      <c r="A242" s="163" t="s">
+      <c r="C273" s="193"/>
+    </row>
+    <row r="274" spans="1:3">
+      <c r="A274" s="163" t="s">
         <v>4336</v>
       </c>
-      <c r="B242" s="163" t="s">
+      <c r="B274" s="163" t="s">
         <v>4484</v>
       </c>
     </row>
-    <row r="244" spans="1:3" s="177" customFormat="1">
-      <c r="A244" s="181" t="s">
+    <row r="276" spans="1:3" s="177" customFormat="1">
+      <c r="A276" s="181" t="s">
         <v>4489</v>
       </c>
     </row>
-    <row r="245" spans="1:3" s="177" customFormat="1" ht="30">
-      <c r="A245" s="177" t="s">
+    <row r="277" spans="1:3" s="177" customFormat="1" ht="30">
+      <c r="A277" s="177" t="s">
         <v>4490</v>
       </c>
-      <c r="B245" s="177" t="s">
+      <c r="B277" s="177" t="s">
         <v>4491</v>
       </c>
     </row>
-    <row r="246" spans="1:3" s="177" customFormat="1">
-      <c r="A246" s="177" t="s">
+    <row r="278" spans="1:3" s="177" customFormat="1">
+      <c r="A278" s="177" t="s">
         <v>4492</v>
       </c>
-      <c r="B246" s="177" t="s">
+      <c r="B278" s="177" t="s">
         <v>4493</v>
       </c>
-      <c r="C246" s="177" t="s">
+      <c r="C278" s="177" t="s">
         <v>4494</v>
       </c>
     </row>
-    <row r="247" spans="1:3" s="177" customFormat="1">
-      <c r="A247" s="177" t="s">
+    <row r="279" spans="1:3" s="177" customFormat="1">
+      <c r="A279" s="177" t="s">
         <v>4495</v>
       </c>
-      <c r="B247" s="177" t="s">
+      <c r="B279" s="177" t="s">
         <v>4496</v>
       </c>
-      <c r="C247" s="177" t="s">
+      <c r="C279" s="177" t="s">
         <v>4497</v>
       </c>
     </row>
-    <row r="248" spans="1:3" s="177" customFormat="1">
-      <c r="A248" s="177" t="s">
+    <row r="280" spans="1:3" s="177" customFormat="1">
+      <c r="A280" s="177" t="s">
         <v>4498</v>
       </c>
-      <c r="B248" s="177" t="s">
+      <c r="B280" s="177" t="s">
         <v>4499</v>
       </c>
-      <c r="C248" s="177" t="s">
+      <c r="C280" s="177" t="s">
         <v>4500</v>
       </c>
     </row>
-    <row r="249" spans="1:3" s="177" customFormat="1"/>
-    <row r="250" spans="1:3" s="177" customFormat="1"/>
-    <row r="252" spans="1:3">
-      <c r="A252" s="181" t="s">
+    <row r="281" spans="1:3" s="177" customFormat="1"/>
+    <row r="282" spans="1:3" s="177" customFormat="1"/>
+    <row r="284" spans="1:3">
+      <c r="A284" s="181" t="s">
         <v>4485</v>
       </c>
     </row>
-    <row r="253" spans="1:3">
-      <c r="A253" s="177" t="s">
+    <row r="285" spans="1:3">
+      <c r="A285" s="177" t="s">
         <v>4336</v>
       </c>
-      <c r="B253" s="163" t="s">
+      <c r="B285" s="163" t="s">
         <v>4486</v>
       </c>
     </row>
-    <row r="254" spans="1:3">
-      <c r="A254" s="163" t="s">
+    <row r="286" spans="1:3">
+      <c r="A286" s="163" t="s">
         <v>4487</v>
       </c>
-      <c r="B254" s="163" t="s">
+      <c r="B286" s="163" t="s">
         <v>4488</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
     <mergeCell ref="A150:C150"/>
     <mergeCell ref="A128:C128"/>
     <mergeCell ref="A3:C3"/>
@@ -33291,16 +33540,17 @@
     <mergeCell ref="A92:C92"/>
     <mergeCell ref="A104:C104"/>
     <mergeCell ref="A155:C155"/>
-    <mergeCell ref="A217:C217"/>
-    <mergeCell ref="A219:C219"/>
+    <mergeCell ref="A249:C249"/>
+    <mergeCell ref="A251:C251"/>
     <mergeCell ref="A185:C185"/>
     <mergeCell ref="A189:C189"/>
     <mergeCell ref="A205:C205"/>
-    <mergeCell ref="C239:C241"/>
-    <mergeCell ref="A236:C236"/>
+    <mergeCell ref="C271:C273"/>
+    <mergeCell ref="A268:C268"/>
     <mergeCell ref="A183:C183"/>
     <mergeCell ref="A169:C169"/>
     <mergeCell ref="A158:C158"/>
+    <mergeCell ref="A216:C216"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A115" r:id="rId1" xr:uid="{43457FE6-F071-49FC-8229-A1C8D22978EB}"/>
@@ -33332,11 +33582,11 @@
       <c r="C1" s="110"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="189" t="s">
+      <c r="A3" s="192" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="189"/>
-      <c r="C3" s="189"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="192"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="112"/>
@@ -33611,11 +33861,11 @@
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="189" t="s">
+      <c r="A42" s="192" t="s">
         <v>60</v>
       </c>
-      <c r="B42" s="189"/>
-      <c r="C42" s="189"/>
+      <c r="B42" s="192"/>
+      <c r="C42" s="192"/>
     </row>
     <row r="43" spans="1:3" ht="30">
       <c r="A43" s="112"/>
@@ -33762,11 +34012,11 @@
       </c>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="189" t="s">
+      <c r="A67" s="192" t="s">
         <v>4310</v>
       </c>
-      <c r="B67" s="189"/>
-      <c r="C67" s="189"/>
+      <c r="B67" s="192"/>
+      <c r="C67" s="192"/>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="160" t="s">
@@ -33880,11 +34130,11 @@
       <c r="C1" s="110"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="189" t="s">
+      <c r="A3" s="192" t="s">
         <v>89</v>
       </c>
-      <c r="B3" s="189"/>
-      <c r="C3" s="189"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="192"/>
     </row>
     <row r="4" spans="1:3" ht="25.5">
       <c r="A4" s="41" t="s">
@@ -34027,87 +34277,87 @@
       <c r="C2" s="112"/>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="192" t="s">
+      <c r="A3" s="195" t="s">
         <v>122</v>
       </c>
-      <c r="B3" s="192"/>
-      <c r="C3" s="192"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="195"/>
     </row>
     <row r="4" spans="1:8" ht="135">
       <c r="A4" s="112"/>
       <c r="B4" s="112" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="190" t="s">
+      <c r="C4" s="193" t="s">
         <v>124</v>
       </c>
-      <c r="D4" s="190"/>
-      <c r="E4" s="190"/>
-      <c r="F4" s="190"/>
-      <c r="G4" s="190"/>
-      <c r="H4" s="190"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
     </row>
     <row r="5" spans="1:8" ht="14.1" customHeight="1">
       <c r="A5" s="112" t="s">
         <v>125</v>
       </c>
-      <c r="B5" s="190" t="s">
+      <c r="B5" s="193" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="190"/>
-      <c r="D5" s="190"/>
-      <c r="E5" s="190"/>
-      <c r="F5" s="190"/>
-      <c r="G5" s="190"/>
-      <c r="H5" s="190"/>
+      <c r="C5" s="193"/>
+      <c r="D5" s="193"/>
+      <c r="E5" s="193"/>
+      <c r="F5" s="193"/>
+      <c r="G5" s="193"/>
+      <c r="H5" s="193"/>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="112" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="190"/>
-      <c r="C6" s="190"/>
-      <c r="D6" s="190"/>
-      <c r="E6" s="190"/>
-      <c r="F6" s="190"/>
-      <c r="G6" s="190"/>
-      <c r="H6" s="190"/>
+      <c r="B6" s="193"/>
+      <c r="C6" s="193"/>
+      <c r="D6" s="193"/>
+      <c r="E6" s="193"/>
+      <c r="F6" s="193"/>
+      <c r="G6" s="193"/>
+      <c r="H6" s="193"/>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="112" t="s">
         <v>128</v>
       </c>
-      <c r="B7" s="190"/>
-      <c r="C7" s="190"/>
-      <c r="D7" s="190"/>
-      <c r="E7" s="190"/>
-      <c r="F7" s="190"/>
-      <c r="G7" s="190"/>
-      <c r="H7" s="190"/>
+      <c r="B7" s="193"/>
+      <c r="C7" s="193"/>
+      <c r="D7" s="193"/>
+      <c r="E7" s="193"/>
+      <c r="F7" s="193"/>
+      <c r="G7" s="193"/>
+      <c r="H7" s="193"/>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="112" t="s">
         <v>129</v>
       </c>
-      <c r="B8" s="190"/>
-      <c r="C8" s="190"/>
-      <c r="D8" s="190"/>
-      <c r="E8" s="190"/>
-      <c r="F8" s="190"/>
-      <c r="G8" s="190"/>
-      <c r="H8" s="190"/>
+      <c r="B8" s="193"/>
+      <c r="C8" s="193"/>
+      <c r="D8" s="193"/>
+      <c r="E8" s="193"/>
+      <c r="F8" s="193"/>
+      <c r="G8" s="193"/>
+      <c r="H8" s="193"/>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="112" t="s">
         <v>130</v>
       </c>
-      <c r="B9" s="190"/>
-      <c r="C9" s="190"/>
-      <c r="D9" s="190"/>
-      <c r="E9" s="190"/>
-      <c r="F9" s="190"/>
-      <c r="G9" s="190"/>
-      <c r="H9" s="190"/>
+      <c r="B9" s="193"/>
+      <c r="C9" s="193"/>
+      <c r="D9" s="193"/>
+      <c r="E9" s="193"/>
+      <c r="F9" s="193"/>
+      <c r="G9" s="193"/>
+      <c r="H9" s="193"/>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="112" t="s">
@@ -34146,10 +34396,10 @@
       <c r="C13" s="112"/>
     </row>
     <row r="16" spans="1:8">
-      <c r="A16" s="192" t="s">
+      <c r="A16" s="195" t="s">
         <v>139</v>
       </c>
-      <c r="B16" s="192"/>
+      <c r="B16" s="195"/>
       <c r="C16" s="111"/>
     </row>
     <row r="17" spans="1:2">
@@ -34330,10 +34580,10 @@
       </c>
     </row>
     <row r="42" spans="1:3">
-      <c r="A42" s="192" t="s">
+      <c r="A42" s="195" t="s">
         <v>184</v>
       </c>
-      <c r="B42" s="192"/>
+      <c r="B42" s="195"/>
       <c r="C42" s="111"/>
     </row>
     <row r="43" spans="1:3">
@@ -34912,10 +35162,10 @@
       <c r="C107" s="112"/>
     </row>
     <row r="108" spans="1:3">
-      <c r="A108" s="192" t="s">
+      <c r="A108" s="195" t="s">
         <v>305</v>
       </c>
-      <c r="B108" s="192"/>
+      <c r="B108" s="195"/>
       <c r="C108" s="111"/>
     </row>
     <row r="109" spans="1:3">
@@ -35011,10 +35261,10 @@
       <c r="C120" s="112"/>
     </row>
     <row r="121" spans="1:3">
-      <c r="A121" s="194" t="s">
+      <c r="A121" s="197" t="s">
         <v>322</v>
       </c>
-      <c r="B121" s="194"/>
+      <c r="B121" s="197"/>
       <c r="C121" s="111"/>
     </row>
     <row r="122" spans="1:3">
@@ -35120,10 +35370,10 @@
       <c r="C133" s="112"/>
     </row>
     <row r="134" spans="1:3">
-      <c r="A134" s="193" t="s">
+      <c r="A134" s="196" t="s">
         <v>344</v>
       </c>
-      <c r="B134" s="193"/>
+      <c r="B134" s="196"/>
       <c r="C134" s="111"/>
     </row>
     <row r="135" spans="1:3">
@@ -35235,10 +35485,10 @@
       <c r="C146" s="112"/>
     </row>
     <row r="149" spans="1:3">
-      <c r="A149" s="192" t="s">
+      <c r="A149" s="195" t="s">
         <v>369</v>
       </c>
-      <c r="B149" s="192"/>
+      <c r="B149" s="195"/>
       <c r="C149" s="111"/>
     </row>
     <row r="150" spans="1:3">
@@ -35301,10 +35551,10 @@
       <c r="C156" s="112"/>
     </row>
     <row r="158" spans="1:3">
-      <c r="A158" s="192" t="s">
+      <c r="A158" s="195" t="s">
         <v>382</v>
       </c>
-      <c r="B158" s="192"/>
+      <c r="B158" s="195"/>
       <c r="C158" s="111"/>
     </row>
     <row r="159" spans="1:3" ht="45">
@@ -35410,10 +35660,10 @@
       <c r="C170" s="112"/>
     </row>
     <row r="171" spans="1:3">
-      <c r="A171" s="192" t="s">
+      <c r="A171" s="195" t="s">
         <v>404</v>
       </c>
-      <c r="B171" s="192"/>
+      <c r="B171" s="195"/>
       <c r="C171" s="111"/>
     </row>
     <row r="172" spans="1:3">
@@ -35659,10 +35909,10 @@
       <c r="C197" s="112"/>
     </row>
     <row r="199" spans="1:3">
-      <c r="A199" s="192" t="s">
+      <c r="A199" s="195" t="s">
         <v>461</v>
       </c>
-      <c r="B199" s="192"/>
+      <c r="B199" s="195"/>
       <c r="C199" s="111"/>
     </row>
     <row r="200" spans="1:3" ht="30">
@@ -35727,10 +35977,10 @@
       <c r="C206" s="112"/>
     </row>
     <row r="207" spans="1:3">
-      <c r="A207" s="192" t="s">
+      <c r="A207" s="195" t="s">
         <v>475</v>
       </c>
-      <c r="B207" s="192"/>
+      <c r="B207" s="195"/>
       <c r="C207" s="111"/>
     </row>
     <row r="208" spans="1:3">
@@ -35907,11 +36157,11 @@
       <c r="C228" s="112"/>
     </row>
     <row r="230" spans="1:3">
-      <c r="A230" s="192" t="s">
+      <c r="A230" s="195" t="s">
         <v>517</v>
       </c>
-      <c r="B230" s="192"/>
-      <c r="C230" s="192"/>
+      <c r="B230" s="195"/>
+      <c r="C230" s="195"/>
     </row>
     <row r="231" spans="1:3">
       <c r="A231" s="6"/>
@@ -36136,10 +36386,10 @@
       <c r="C258" s="112"/>
     </row>
     <row r="260" spans="1:3">
-      <c r="A260" s="193" t="s">
+      <c r="A260" s="196" t="s">
         <v>567</v>
       </c>
-      <c r="B260" s="193"/>
+      <c r="B260" s="196"/>
       <c r="C260" s="111"/>
     </row>
     <row r="261" spans="1:3">
@@ -36215,10 +36465,10 @@
       <c r="C268" s="112"/>
     </row>
     <row r="271" spans="1:3">
-      <c r="A271" s="192" t="s">
+      <c r="A271" s="195" t="s">
         <v>584</v>
       </c>
-      <c r="B271" s="192"/>
+      <c r="B271" s="195"/>
       <c r="C271" s="111"/>
     </row>
     <row r="272" spans="1:3" ht="30">
@@ -36312,10 +36562,10 @@
       <c r="C281" s="112"/>
     </row>
     <row r="284" spans="1:3">
-      <c r="A284" s="192" t="s">
+      <c r="A284" s="195" t="s">
         <v>605</v>
       </c>
-      <c r="B284" s="192"/>
+      <c r="B284" s="195"/>
       <c r="C284" s="111"/>
     </row>
     <row r="285" spans="1:3">
@@ -36382,10 +36632,10 @@
       <c r="C291" s="112"/>
     </row>
     <row r="295" spans="1:3">
-      <c r="A295" s="192" t="s">
+      <c r="A295" s="195" t="s">
         <v>620</v>
       </c>
-      <c r="B295" s="192"/>
+      <c r="B295" s="195"/>
       <c r="C295" s="111"/>
     </row>
     <row r="296" spans="1:3">
@@ -36673,11 +36923,11 @@
       <c r="C329" s="112"/>
     </row>
     <row r="330" spans="1:3">
-      <c r="A330" s="193" t="s">
+      <c r="A330" s="196" t="s">
         <v>686</v>
       </c>
-      <c r="B330" s="193"/>
-      <c r="C330" s="193"/>
+      <c r="B330" s="196"/>
+      <c r="C330" s="196"/>
     </row>
     <row r="331" spans="1:3">
       <c r="A331" s="112" t="s">
@@ -36716,11 +36966,11 @@
       <c r="C334" s="112"/>
     </row>
     <row r="340" spans="1:3">
-      <c r="A340" s="192" t="s">
+      <c r="A340" s="195" t="s">
         <v>695</v>
       </c>
-      <c r="B340" s="192"/>
-      <c r="C340" s="192"/>
+      <c r="B340" s="195"/>
+      <c r="C340" s="195"/>
     </row>
     <row r="341" spans="1:3" ht="30">
       <c r="A341" s="112"/>
@@ -36822,18 +37072,18 @@
       <c r="C353" s="112"/>
     </row>
     <row r="360" spans="1:3">
-      <c r="A360" s="188" t="s">
+      <c r="A360" s="191" t="s">
         <v>712</v>
       </c>
-      <c r="B360" s="188"/>
-      <c r="C360" s="188"/>
+      <c r="B360" s="191"/>
+      <c r="C360" s="191"/>
     </row>
     <row r="361" spans="1:3">
-      <c r="A361" s="192" t="s">
+      <c r="A361" s="195" t="s">
         <v>713</v>
       </c>
-      <c r="B361" s="192"/>
-      <c r="C361" s="192"/>
+      <c r="B361" s="195"/>
+      <c r="C361" s="195"/>
     </row>
     <row r="362" spans="1:3">
       <c r="A362" s="112"/>
@@ -36945,11 +37195,11 @@
       <c r="C374" s="112"/>
     </row>
     <row r="378" spans="1:3">
-      <c r="A378" s="188" t="s">
+      <c r="A378" s="191" t="s">
         <v>736</v>
       </c>
-      <c r="B378" s="188"/>
-      <c r="C378" s="188"/>
+      <c r="B378" s="191"/>
+      <c r="C378" s="191"/>
     </row>
     <row r="379" spans="1:3">
       <c r="A379" s="112"/>
@@ -37234,11 +37484,11 @@
       <c r="C412" s="112"/>
     </row>
     <row r="413" spans="1:3">
-      <c r="A413" s="195" t="s">
+      <c r="A413" s="198" t="s">
         <v>801</v>
       </c>
-      <c r="B413" s="195"/>
-      <c r="C413" s="195"/>
+      <c r="B413" s="198"/>
+      <c r="C413" s="198"/>
     </row>
     <row r="414" spans="1:3">
       <c r="A414" s="27"/>
@@ -37336,11 +37586,11 @@
       <c r="C424" s="112"/>
     </row>
     <row r="425" spans="1:3">
-      <c r="A425" s="188" t="s">
+      <c r="A425" s="191" t="s">
         <v>822</v>
       </c>
-      <c r="B425" s="188"/>
-      <c r="C425" s="188"/>
+      <c r="B425" s="191"/>
+      <c r="C425" s="191"/>
     </row>
     <row r="426" spans="1:3">
       <c r="A426" s="112"/>
@@ -37548,11 +37798,11 @@
       <c r="C451" s="112"/>
     </row>
     <row r="452" spans="1:3">
-      <c r="A452" s="188" t="s">
+      <c r="A452" s="191" t="s">
         <v>863</v>
       </c>
-      <c r="B452" s="188"/>
-      <c r="C452" s="188"/>
+      <c r="B452" s="191"/>
+      <c r="C452" s="191"/>
     </row>
     <row r="453" spans="1:3">
       <c r="A453" s="112"/>
@@ -37657,11 +37907,11 @@
       <c r="C464" s="112"/>
     </row>
     <row r="467" spans="1:3">
-      <c r="A467" s="192" t="s">
+      <c r="A467" s="195" t="s">
         <v>885</v>
       </c>
-      <c r="B467" s="192"/>
-      <c r="C467" s="192"/>
+      <c r="B467" s="195"/>
+      <c r="C467" s="195"/>
     </row>
     <row r="468" spans="1:3">
       <c r="A468" s="112"/>
@@ -37886,11 +38136,11 @@
       <c r="C495" s="112"/>
     </row>
     <row r="496" spans="1:3">
-      <c r="A496" s="188" t="s">
+      <c r="A496" s="191" t="s">
         <v>921</v>
       </c>
-      <c r="B496" s="188"/>
-      <c r="C496" s="188"/>
+      <c r="B496" s="191"/>
+      <c r="C496" s="191"/>
     </row>
     <row r="498" spans="1:3">
       <c r="A498" s="112" t="s">
@@ -37938,7 +38188,7 @@
       </c>
     </row>
     <row r="503" spans="1:3" ht="45">
-      <c r="A503" s="190" t="s">
+      <c r="A503" s="193" t="s">
         <v>932</v>
       </c>
       <c r="B503" s="112" t="s">
@@ -37949,7 +38199,7 @@
       </c>
     </row>
     <row r="504" spans="1:3" ht="45">
-      <c r="A504" s="190"/>
+      <c r="A504" s="193"/>
       <c r="B504" s="112" t="s">
         <v>934</v>
       </c>
@@ -37974,11 +38224,11 @@
       <c r="C507" s="112"/>
     </row>
     <row r="510" spans="1:3">
-      <c r="A510" s="192" t="s">
+      <c r="A510" s="195" t="s">
         <v>938</v>
       </c>
-      <c r="B510" s="192"/>
-      <c r="C510" s="192"/>
+      <c r="B510" s="195"/>
+      <c r="C510" s="195"/>
     </row>
     <row r="512" spans="1:3" ht="45">
       <c r="A512" s="112" t="s">
@@ -38131,18 +38381,18 @@
       <c r="C533" s="112"/>
     </row>
     <row r="536" spans="1:3">
-      <c r="A536" s="188" t="s">
+      <c r="A536" s="191" t="s">
         <v>966</v>
       </c>
-      <c r="B536" s="188"/>
-      <c r="C536" s="188"/>
+      <c r="B536" s="191"/>
+      <c r="C536" s="191"/>
     </row>
     <row r="537" spans="1:3">
-      <c r="A537" s="192" t="s">
+      <c r="A537" s="195" t="s">
         <v>967</v>
       </c>
-      <c r="B537" s="192"/>
-      <c r="C537" s="192"/>
+      <c r="B537" s="195"/>
+      <c r="C537" s="195"/>
     </row>
     <row r="538" spans="1:3">
       <c r="A538" s="112"/>
@@ -38235,11 +38485,11 @@
       <c r="C548" s="112"/>
     </row>
     <row r="551" spans="1:3">
-      <c r="A551" s="192" t="s">
+      <c r="A551" s="195" t="s">
         <v>988</v>
       </c>
-      <c r="B551" s="192"/>
-      <c r="C551" s="192"/>
+      <c r="B551" s="195"/>
+      <c r="C551" s="195"/>
     </row>
     <row r="552" spans="1:3">
       <c r="A552" s="112" t="s">
@@ -38401,11 +38651,11 @@
       <c r="C572" s="112"/>
     </row>
     <row r="576" spans="1:3">
-      <c r="A576" s="192" t="s">
+      <c r="A576" s="195" t="s">
         <v>1015</v>
       </c>
-      <c r="B576" s="192"/>
-      <c r="C576" s="192"/>
+      <c r="B576" s="195"/>
+      <c r="C576" s="195"/>
     </row>
     <row r="577" spans="1:3">
       <c r="A577" s="112"/>
@@ -38525,11 +38775,11 @@
       </c>
     </row>
     <row r="592" spans="1:3">
-      <c r="A592" s="192" t="s">
+      <c r="A592" s="195" t="s">
         <v>1037</v>
       </c>
-      <c r="B592" s="192"/>
-      <c r="C592" s="192"/>
+      <c r="B592" s="195"/>
+      <c r="C592" s="195"/>
     </row>
     <row r="593" spans="1:2">
       <c r="A593" s="112"/>
@@ -38694,11 +38944,11 @@
       <c r="C612" s="112"/>
     </row>
     <row r="615" spans="1:3">
-      <c r="A615" s="192" t="s">
+      <c r="A615" s="195" t="s">
         <v>1077</v>
       </c>
-      <c r="B615" s="192"/>
-      <c r="C615" s="192"/>
+      <c r="B615" s="195"/>
+      <c r="C615" s="195"/>
     </row>
     <row r="616" spans="1:3" ht="60">
       <c r="A616" s="112" t="s">
@@ -38854,11 +39104,11 @@
       <c r="C633" s="112"/>
     </row>
     <row r="635" spans="1:3">
-      <c r="A635" s="188" t="s">
+      <c r="A635" s="191" t="s">
         <v>1110</v>
       </c>
-      <c r="B635" s="188"/>
-      <c r="C635" s="188"/>
+      <c r="B635" s="191"/>
+      <c r="C635" s="191"/>
     </row>
     <row r="636" spans="1:3">
       <c r="A636" s="112"/>
@@ -39153,41 +39403,41 @@
       </c>
     </row>
     <row r="670" spans="1:3">
-      <c r="A670" s="202" t="s">
+      <c r="A670" s="205" t="s">
         <v>1169</v>
       </c>
-      <c r="B670" s="202" t="s">
+      <c r="B670" s="205" t="s">
         <v>1170</v>
       </c>
-      <c r="C670" s="199" t="s">
+      <c r="C670" s="202" t="s">
         <v>1171</v>
       </c>
     </row>
     <row r="671" spans="1:3">
-      <c r="A671" s="202"/>
-      <c r="B671" s="202"/>
-      <c r="C671" s="200"/>
+      <c r="A671" s="205"/>
+      <c r="B671" s="205"/>
+      <c r="C671" s="203"/>
     </row>
     <row r="672" spans="1:3">
-      <c r="A672" s="202"/>
-      <c r="B672" s="202"/>
-      <c r="C672" s="201"/>
+      <c r="A672" s="205"/>
+      <c r="B672" s="205"/>
+      <c r="C672" s="204"/>
     </row>
     <row r="673" spans="1:3">
-      <c r="A673" s="202" t="s">
+      <c r="A673" s="205" t="s">
         <v>1172</v>
       </c>
-      <c r="B673" s="202" t="s">
+      <c r="B673" s="205" t="s">
         <v>1173</v>
       </c>
-      <c r="C673" s="199" t="s">
+      <c r="C673" s="202" t="s">
         <v>1174</v>
       </c>
     </row>
     <row r="674" spans="1:3" ht="28.15" customHeight="1">
-      <c r="A674" s="202"/>
-      <c r="B674" s="202"/>
-      <c r="C674" s="201"/>
+      <c r="A674" s="205"/>
+      <c r="B674" s="205"/>
+      <c r="C674" s="204"/>
     </row>
     <row r="675" spans="1:3" ht="30">
       <c r="A675" s="114" t="s">
@@ -39199,11 +39449,11 @@
       <c r="C675" s="114"/>
     </row>
     <row r="676" spans="1:3">
-      <c r="A676" s="203" t="s">
+      <c r="A676" s="206" t="s">
         <v>1131</v>
       </c>
-      <c r="B676" s="203"/>
-      <c r="C676" s="203"/>
+      <c r="B676" s="206"/>
+      <c r="C676" s="206"/>
     </row>
     <row r="677" spans="1:3" ht="45">
       <c r="A677" s="112" t="s">
@@ -39373,11 +39623,11 @@
       <c r="B700" s="112"/>
     </row>
     <row r="714" spans="1:3">
-      <c r="A714" s="192" t="s">
+      <c r="A714" s="195" t="s">
         <v>1208</v>
       </c>
-      <c r="B714" s="192"/>
-      <c r="C714" s="192"/>
+      <c r="B714" s="195"/>
+      <c r="C714" s="195"/>
     </row>
     <row r="715" spans="1:3">
       <c r="A715" s="112"/>
@@ -39487,11 +39737,11 @@
       <c r="C729" s="112"/>
     </row>
     <row r="730" spans="1:3">
-      <c r="A730" s="196" t="s">
+      <c r="A730" s="199" t="s">
         <v>1218</v>
       </c>
-      <c r="B730" s="196"/>
-      <c r="C730" s="196"/>
+      <c r="B730" s="199"/>
+      <c r="C730" s="199"/>
     </row>
     <row r="731" spans="1:3" ht="30">
       <c r="A731" s="112"/>
@@ -39522,7 +39772,7 @@
       <c r="A734" s="112" t="s">
         <v>1224</v>
       </c>
-      <c r="B734" s="190" t="s">
+      <c r="B734" s="193" t="s">
         <v>1225</v>
       </c>
       <c r="C734" s="112"/>
@@ -39531,28 +39781,28 @@
       <c r="A735" s="32" t="s">
         <v>1226</v>
       </c>
-      <c r="B735" s="190"/>
+      <c r="B735" s="193"/>
       <c r="C735" s="112"/>
     </row>
     <row r="736" spans="1:3">
       <c r="A736" s="32" t="s">
         <v>1227</v>
       </c>
-      <c r="B736" s="190"/>
+      <c r="B736" s="193"/>
       <c r="C736" s="112"/>
     </row>
     <row r="737" spans="1:3">
       <c r="A737" s="32" t="s">
         <v>1228</v>
       </c>
-      <c r="B737" s="190"/>
+      <c r="B737" s="193"/>
       <c r="C737" s="112"/>
     </row>
     <row r="738" spans="1:3">
       <c r="A738" s="32" t="s">
         <v>1229</v>
       </c>
-      <c r="B738" s="190"/>
+      <c r="B738" s="193"/>
       <c r="C738" s="112"/>
     </row>
     <row r="739" spans="1:3">
@@ -39581,16 +39831,16 @@
       <c r="C741" s="112"/>
     </row>
     <row r="742" spans="1:3">
-      <c r="A742" s="197" t="s">
+      <c r="A742" s="200" t="s">
         <v>1235</v>
       </c>
-      <c r="B742" s="198"/>
-      <c r="C742" s="198"/>
+      <c r="B742" s="201"/>
+      <c r="C742" s="201"/>
     </row>
     <row r="743" spans="1:3">
-      <c r="A743" s="198"/>
-      <c r="B743" s="198"/>
-      <c r="C743" s="198"/>
+      <c r="A743" s="201"/>
+      <c r="B743" s="201"/>
+      <c r="C743" s="201"/>
     </row>
   </sheetData>
   <mergeCells count="48">
@@ -39694,7 +39944,7 @@
       <c r="A4" s="115" t="s">
         <v>1241</v>
       </c>
-      <c r="B4" s="204" t="s">
+      <c r="B4" s="207" t="s">
         <v>1242</v>
       </c>
       <c r="C4" s="115"/>
@@ -39703,7 +39953,7 @@
       <c r="A5" s="115" t="s">
         <v>1243</v>
       </c>
-      <c r="B5" s="204"/>
+      <c r="B5" s="207"/>
       <c r="C5" s="115"/>
     </row>
     <row r="6" spans="1:3">
@@ -39743,17 +39993,17 @@
       <c r="C9" s="115"/>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="205" t="s">
+      <c r="A14" s="208" t="s">
         <v>1252</v>
       </c>
-      <c r="B14" s="205"/>
-      <c r="C14" s="205"/>
+      <c r="B14" s="208"/>
+      <c r="C14" s="208"/>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="115" t="s">
         <v>1253</v>
       </c>
-      <c r="B15" s="190" t="s">
+      <c r="B15" s="193" t="s">
         <v>1254</v>
       </c>
       <c r="C15" s="115"/>
@@ -39762,7 +40012,7 @@
       <c r="A16" s="115" t="s">
         <v>1255</v>
       </c>
-      <c r="B16" s="204"/>
+      <c r="B16" s="207"/>
       <c r="C16" s="115"/>
     </row>
     <row r="17" spans="1:2" ht="61.15" customHeight="1">
@@ -39846,11 +40096,11 @@
       <c r="B29" s="115"/>
     </row>
     <row r="35" spans="1:3">
-      <c r="A35" s="205" t="s">
+      <c r="A35" s="208" t="s">
         <v>1270</v>
       </c>
-      <c r="B35" s="205"/>
-      <c r="C35" s="205"/>
+      <c r="B35" s="208"/>
+      <c r="C35" s="208"/>
     </row>
     <row r="36" spans="1:3">
       <c r="A36" s="115" t="s">
@@ -39899,11 +40149,11 @@
       <c r="C47" s="115"/>
     </row>
     <row r="54" spans="1:3">
-      <c r="A54" s="186" t="s">
+      <c r="A54" s="189" t="s">
         <v>1279</v>
       </c>
-      <c r="B54" s="186"/>
-      <c r="C54" s="186"/>
+      <c r="B54" s="189"/>
+      <c r="C54" s="189"/>
     </row>
     <row r="56" spans="1:3">
       <c r="A56" s="115" t="s">
@@ -39940,11 +40190,11 @@
       <c r="C59" s="115"/>
     </row>
     <row r="61" spans="1:3">
-      <c r="A61" s="186" t="s">
+      <c r="A61" s="189" t="s">
         <v>885</v>
       </c>
-      <c r="B61" s="186"/>
-      <c r="C61" s="186"/>
+      <c r="B61" s="189"/>
+      <c r="C61" s="189"/>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" s="115"/>
@@ -39981,11 +40231,11 @@
       <c r="C65" s="115"/>
     </row>
     <row r="71" spans="1:3">
-      <c r="A71" s="205" t="s">
+      <c r="A71" s="208" t="s">
         <v>1288</v>
       </c>
-      <c r="B71" s="205"/>
-      <c r="C71" s="205"/>
+      <c r="B71" s="208"/>
+      <c r="C71" s="208"/>
     </row>
     <row r="73" spans="1:3" ht="195">
       <c r="A73" s="112" t="s">
@@ -40051,11 +40301,11 @@
       <c r="C79" s="115"/>
     </row>
     <row r="82" spans="1:5">
-      <c r="A82" s="205" t="s">
+      <c r="A82" s="208" t="s">
         <v>1302</v>
       </c>
-      <c r="B82" s="205"/>
-      <c r="C82" s="205"/>
+      <c r="B82" s="208"/>
+      <c r="C82" s="208"/>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="112"/>
@@ -40130,10 +40380,10 @@
       <c r="B89" s="112" t="s">
         <v>1316</v>
       </c>
-      <c r="C89" s="206" t="s">
+      <c r="C89" s="209" t="s">
         <v>1317</v>
       </c>
-      <c r="D89" s="208" t="s">
+      <c r="D89" s="211" t="s">
         <v>1318</v>
       </c>
       <c r="E89" s="117" t="s">
@@ -40147,8 +40397,8 @@
       <c r="B90" s="112" t="s">
         <v>1321</v>
       </c>
-      <c r="C90" s="206"/>
-      <c r="D90" s="208"/>
+      <c r="C90" s="209"/>
+      <c r="D90" s="211"/>
       <c r="E90" s="117"/>
     </row>
     <row r="91" spans="1:5">
@@ -40158,8 +40408,8 @@
       <c r="B91" s="112" t="s">
         <v>1323</v>
       </c>
-      <c r="C91" s="206"/>
-      <c r="D91" s="208"/>
+      <c r="C91" s="209"/>
+      <c r="D91" s="211"/>
       <c r="E91" s="117"/>
     </row>
     <row r="92" spans="1:5" ht="30">
@@ -40169,8 +40419,8 @@
       <c r="B92" s="112" t="s">
         <v>1325</v>
       </c>
-      <c r="C92" s="206"/>
-      <c r="D92" s="208"/>
+      <c r="C92" s="209"/>
+      <c r="D92" s="211"/>
       <c r="E92" s="117"/>
     </row>
     <row r="93" spans="1:5" ht="30">
@@ -40180,8 +40430,8 @@
       <c r="B93" s="112" t="s">
         <v>1327</v>
       </c>
-      <c r="C93" s="206"/>
-      <c r="D93" s="208"/>
+      <c r="C93" s="209"/>
+      <c r="D93" s="211"/>
       <c r="E93" s="117"/>
     </row>
     <row r="94" spans="1:5" ht="30">
@@ -40191,8 +40441,8 @@
       <c r="B94" s="112" t="s">
         <v>1329</v>
       </c>
-      <c r="C94" s="206"/>
-      <c r="D94" s="208"/>
+      <c r="C94" s="209"/>
+      <c r="D94" s="211"/>
       <c r="E94" s="117"/>
     </row>
     <row r="95" spans="1:5">
@@ -40202,8 +40452,8 @@
       <c r="B95" s="112" t="s">
         <v>1331</v>
       </c>
-      <c r="C95" s="206"/>
-      <c r="D95" s="208"/>
+      <c r="C95" s="209"/>
+      <c r="D95" s="211"/>
       <c r="E95" s="117"/>
     </row>
     <row r="96" spans="1:5">
@@ -40213,8 +40463,8 @@
       <c r="B96" s="112" t="s">
         <v>1333</v>
       </c>
-      <c r="C96" s="206"/>
-      <c r="D96" s="208"/>
+      <c r="C96" s="209"/>
+      <c r="D96" s="211"/>
       <c r="E96" s="117"/>
     </row>
     <row r="97" spans="1:5">
@@ -40224,8 +40474,8 @@
       <c r="B97" s="112" t="s">
         <v>1335</v>
       </c>
-      <c r="C97" s="206"/>
-      <c r="D97" s="208"/>
+      <c r="C97" s="209"/>
+      <c r="D97" s="211"/>
       <c r="E97" s="117"/>
     </row>
     <row r="98" spans="1:5" ht="30">
@@ -40235,8 +40485,8 @@
       <c r="B98" s="112" t="s">
         <v>1337</v>
       </c>
-      <c r="C98" s="206"/>
-      <c r="D98" s="208"/>
+      <c r="C98" s="209"/>
+      <c r="D98" s="211"/>
       <c r="E98" s="117"/>
     </row>
     <row r="99" spans="1:5">
@@ -40246,8 +40496,8 @@
       <c r="B99" s="112" t="s">
         <v>718</v>
       </c>
-      <c r="C99" s="206"/>
-      <c r="D99" s="208"/>
+      <c r="C99" s="209"/>
+      <c r="D99" s="211"/>
       <c r="E99" s="117"/>
     </row>
     <row r="100" spans="1:5" ht="30">
@@ -40257,8 +40507,8 @@
       <c r="B100" s="112" t="s">
         <v>1340</v>
       </c>
-      <c r="C100" s="206"/>
-      <c r="D100" s="208"/>
+      <c r="C100" s="209"/>
+      <c r="D100" s="211"/>
       <c r="E100" s="117" t="s">
         <v>1341</v>
       </c>
@@ -40270,8 +40520,8 @@
       <c r="B101" s="112" t="s">
         <v>1343</v>
       </c>
-      <c r="C101" s="206"/>
-      <c r="D101" s="208"/>
+      <c r="C101" s="209"/>
+      <c r="D101" s="211"/>
       <c r="E101" s="117" t="s">
         <v>1344</v>
       </c>
@@ -40437,10 +40687,10 @@
       <c r="B116" s="112" t="s">
         <v>1373</v>
       </c>
-      <c r="C116" s="206" t="s">
+      <c r="C116" s="209" t="s">
         <v>1374</v>
       </c>
-      <c r="D116" s="208" t="s">
+      <c r="D116" s="211" t="s">
         <v>1375</v>
       </c>
       <c r="E116" s="117" t="s">
@@ -40454,8 +40704,8 @@
       <c r="B117" s="112" t="s">
         <v>1378</v>
       </c>
-      <c r="C117" s="206"/>
-      <c r="D117" s="208"/>
+      <c r="C117" s="209"/>
+      <c r="D117" s="211"/>
       <c r="E117" s="117" t="s">
         <v>1379</v>
       </c>
@@ -40467,8 +40717,8 @@
       <c r="B118" s="112" t="s">
         <v>1381</v>
       </c>
-      <c r="C118" s="206"/>
-      <c r="D118" s="208"/>
+      <c r="C118" s="209"/>
+      <c r="D118" s="211"/>
       <c r="E118" s="117" t="s">
         <v>1382</v>
       </c>
@@ -40589,10 +40839,10 @@
       <c r="B128" s="112" t="s">
         <v>1407</v>
       </c>
-      <c r="C128" s="206" t="s">
+      <c r="C128" s="209" t="s">
         <v>1408</v>
       </c>
-      <c r="D128" s="208" t="s">
+      <c r="D128" s="211" t="s">
         <v>1409</v>
       </c>
       <c r="E128" s="117" t="s">
@@ -40606,8 +40856,8 @@
       <c r="B129" s="112" t="s">
         <v>1412</v>
       </c>
-      <c r="C129" s="206"/>
-      <c r="D129" s="208"/>
+      <c r="C129" s="209"/>
+      <c r="D129" s="211"/>
       <c r="E129" s="117" t="s">
         <v>1413</v>
       </c>
@@ -40653,13 +40903,13 @@
       <c r="B132" s="112" t="s">
         <v>1425</v>
       </c>
-      <c r="C132" s="206" t="s">
+      <c r="C132" s="209" t="s">
         <v>1426</v>
       </c>
       <c r="D132" s="118" t="s">
         <v>1427</v>
       </c>
-      <c r="E132" s="209" t="s">
+      <c r="E132" s="212" t="s">
         <v>1428</v>
       </c>
     </row>
@@ -40670,11 +40920,11 @@
       <c r="B133" s="112" t="s">
         <v>1430</v>
       </c>
-      <c r="C133" s="206"/>
+      <c r="C133" s="209"/>
       <c r="D133" s="118" t="s">
         <v>1431</v>
       </c>
-      <c r="E133" s="209"/>
+      <c r="E133" s="212"/>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="118" t="s">
@@ -40852,18 +41102,18 @@
       <c r="C148" s="112"/>
     </row>
     <row r="149" spans="1:4">
-      <c r="A149" s="188" t="s">
+      <c r="A149" s="191" t="s">
         <v>1468</v>
       </c>
-      <c r="B149" s="188"/>
-      <c r="C149" s="188"/>
+      <c r="B149" s="191"/>
+      <c r="C149" s="191"/>
     </row>
     <row r="150" spans="1:4">
-      <c r="A150" s="192" t="s">
+      <c r="A150" s="195" t="s">
         <v>1469</v>
       </c>
-      <c r="B150" s="192"/>
-      <c r="C150" s="192"/>
+      <c r="B150" s="195"/>
+      <c r="C150" s="195"/>
     </row>
     <row r="151" spans="1:4" ht="30">
       <c r="A151" s="112" t="s">
@@ -41019,18 +41269,18 @@
       <c r="C167" s="115"/>
     </row>
     <row r="170" spans="1:3">
-      <c r="A170" s="205" t="s">
+      <c r="A170" s="208" t="s">
         <v>1365</v>
       </c>
-      <c r="B170" s="205"/>
-      <c r="C170" s="205"/>
+      <c r="B170" s="208"/>
+      <c r="C170" s="208"/>
     </row>
     <row r="171" spans="1:3">
-      <c r="A171" s="186" t="s">
+      <c r="A171" s="189" t="s">
         <v>1501</v>
       </c>
-      <c r="B171" s="186"/>
-      <c r="C171" s="186"/>
+      <c r="B171" s="189"/>
+      <c r="C171" s="189"/>
     </row>
     <row r="172" spans="1:3" ht="30">
       <c r="A172" s="115"/>
@@ -41276,11 +41526,11 @@
       <c r="C198" s="115"/>
     </row>
     <row r="200" spans="1:3">
-      <c r="A200" s="186" t="s">
+      <c r="A200" s="189" t="s">
         <v>1554</v>
       </c>
-      <c r="B200" s="186"/>
-      <c r="C200" s="186"/>
+      <c r="B200" s="189"/>
+      <c r="C200" s="189"/>
     </row>
     <row r="201" spans="1:3">
       <c r="A201" s="41" t="s">
@@ -41743,11 +41993,11 @@
       </c>
     </row>
     <row r="245" spans="1:3">
-      <c r="A245" s="186" t="s">
+      <c r="A245" s="189" t="s">
         <v>1644</v>
       </c>
-      <c r="B245" s="186"/>
-      <c r="C245" s="186"/>
+      <c r="B245" s="189"/>
+      <c r="C245" s="189"/>
     </row>
     <row r="246" spans="1:3" ht="45">
       <c r="A246" s="112" t="s">
@@ -41881,11 +42131,11 @@
       <c r="C260" s="115"/>
     </row>
     <row r="261" spans="1:3">
-      <c r="A261" s="205" t="s">
+      <c r="A261" s="208" t="s">
         <v>1671</v>
       </c>
-      <c r="B261" s="205"/>
-      <c r="C261" s="205"/>
+      <c r="B261" s="208"/>
+      <c r="C261" s="208"/>
     </row>
     <row r="262" spans="1:3" ht="60">
       <c r="A262" s="112"/>
@@ -41895,11 +42145,11 @@
       <c r="C262" s="112"/>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="210" t="s">
+      <c r="A263" s="213" t="s">
         <v>1673</v>
       </c>
-      <c r="B263" s="210"/>
-      <c r="C263" s="210"/>
+      <c r="B263" s="213"/>
+      <c r="C263" s="213"/>
     </row>
     <row r="264" spans="1:3">
       <c r="A264" s="112" t="s">
@@ -41927,7 +42177,7 @@
       <c r="C266" s="112"/>
     </row>
     <row r="267" spans="1:3" ht="30">
-      <c r="A267" s="190" t="s">
+      <c r="A267" s="193" t="s">
         <v>1679</v>
       </c>
       <c r="B267" s="112" t="s">
@@ -41936,49 +42186,49 @@
       <c r="C267" s="112"/>
     </row>
     <row r="268" spans="1:3" ht="75">
-      <c r="A268" s="190"/>
+      <c r="A268" s="193"/>
       <c r="B268" s="112" t="s">
         <v>1681</v>
       </c>
       <c r="C268" s="112"/>
     </row>
     <row r="269" spans="1:3" ht="150">
-      <c r="A269" s="190"/>
+      <c r="A269" s="193"/>
       <c r="B269" s="112" t="s">
         <v>1682</v>
       </c>
       <c r="C269" s="112"/>
     </row>
     <row r="270" spans="1:3" ht="90">
-      <c r="A270" s="190"/>
+      <c r="A270" s="193"/>
       <c r="B270" s="112" t="s">
         <v>1683</v>
       </c>
       <c r="C270" s="112"/>
     </row>
     <row r="271" spans="1:3" ht="135">
-      <c r="A271" s="190"/>
+      <c r="A271" s="193"/>
       <c r="B271" s="112" t="s">
         <v>1684</v>
       </c>
       <c r="C271" s="112"/>
     </row>
     <row r="272" spans="1:3" ht="90">
-      <c r="A272" s="190"/>
+      <c r="A272" s="193"/>
       <c r="B272" s="112" t="s">
         <v>1685</v>
       </c>
       <c r="C272" s="112"/>
     </row>
     <row r="273" spans="1:3" ht="120">
-      <c r="A273" s="190"/>
+      <c r="A273" s="193"/>
       <c r="B273" s="112" t="s">
         <v>1686</v>
       </c>
       <c r="C273" s="112"/>
     </row>
     <row r="274" spans="1:3" ht="75">
-      <c r="A274" s="190"/>
+      <c r="A274" s="193"/>
       <c r="B274" s="112" t="s">
         <v>1687</v>
       </c>
@@ -42039,11 +42289,11 @@
       <c r="C281" s="115"/>
     </row>
     <row r="286" spans="1:3">
-      <c r="A286" s="207" t="s">
+      <c r="A286" s="210" t="s">
         <v>1699</v>
       </c>
-      <c r="B286" s="207"/>
-      <c r="C286" s="207"/>
+      <c r="B286" s="210"/>
+      <c r="C286" s="210"/>
     </row>
     <row r="287" spans="1:3">
       <c r="A287" s="41" t="s">
@@ -42310,11 +42560,11 @@
       </c>
     </row>
     <row r="312" spans="1:3">
-      <c r="A312" s="205" t="s">
+      <c r="A312" s="208" t="s">
         <v>1772</v>
       </c>
-      <c r="B312" s="205"/>
-      <c r="C312" s="205"/>
+      <c r="B312" s="208"/>
+      <c r="C312" s="208"/>
     </row>
     <row r="313" spans="1:3">
       <c r="A313" s="115"/>
@@ -42324,11 +42574,11 @@
       <c r="C313" s="115"/>
     </row>
     <row r="314" spans="1:3">
-      <c r="A314" s="186" t="s">
+      <c r="A314" s="189" t="s">
         <v>1774</v>
       </c>
-      <c r="B314" s="186"/>
-      <c r="C314" s="186"/>
+      <c r="B314" s="189"/>
+      <c r="C314" s="189"/>
     </row>
     <row r="315" spans="1:3">
       <c r="A315" s="115" t="s">
@@ -42385,11 +42635,11 @@
       <c r="C320" s="115"/>
     </row>
     <row r="322" spans="1:3">
-      <c r="A322" s="186" t="s">
+      <c r="A322" s="189" t="s">
         <v>1786</v>
       </c>
-      <c r="B322" s="186"/>
-      <c r="C322" s="186"/>
+      <c r="B322" s="189"/>
+      <c r="C322" s="189"/>
     </row>
     <row r="323" spans="1:3">
       <c r="A323" s="23" t="s">
@@ -42590,18 +42840,18 @@
       </c>
     </row>
     <row r="342" spans="1:3">
-      <c r="A342" s="205" t="s">
+      <c r="A342" s="208" t="s">
         <v>1832</v>
       </c>
-      <c r="B342" s="205"/>
-      <c r="C342" s="205"/>
+      <c r="B342" s="208"/>
+      <c r="C342" s="208"/>
     </row>
     <row r="344" spans="1:3">
-      <c r="A344" s="186" t="s">
+      <c r="A344" s="189" t="s">
         <v>1833</v>
       </c>
-      <c r="B344" s="186"/>
-      <c r="C344" s="186"/>
+      <c r="B344" s="189"/>
+      <c r="C344" s="189"/>
     </row>
     <row r="345" spans="1:3" ht="30">
       <c r="A345" s="112" t="s">
@@ -42658,11 +42908,11 @@
       <c r="C350" s="115"/>
     </row>
     <row r="352" spans="1:3">
-      <c r="A352" s="186" t="s">
+      <c r="A352" s="189" t="s">
         <v>1846</v>
       </c>
-      <c r="B352" s="186"/>
-      <c r="C352" s="186"/>
+      <c r="B352" s="189"/>
+      <c r="C352" s="189"/>
     </row>
     <row r="353" spans="1:3">
       <c r="A353" s="23" t="s">
@@ -42863,18 +43113,18 @@
       </c>
     </row>
     <row r="373" spans="1:3">
-      <c r="A373" s="205" t="s">
+      <c r="A373" s="208" t="s">
         <v>1896</v>
       </c>
-      <c r="B373" s="205"/>
-      <c r="C373" s="205"/>
+      <c r="B373" s="208"/>
+      <c r="C373" s="208"/>
     </row>
     <row r="375" spans="1:3">
-      <c r="A375" s="186" t="s">
+      <c r="A375" s="189" t="s">
         <v>1897</v>
       </c>
-      <c r="B375" s="186"/>
-      <c r="C375" s="186"/>
+      <c r="B375" s="189"/>
+      <c r="C375" s="189"/>
     </row>
     <row r="376" spans="1:3">
       <c r="A376" s="115" t="s">
@@ -43098,11 +43348,11 @@
       <c r="C398" s="115"/>
     </row>
     <row r="399" spans="1:3">
-      <c r="A399" s="186" t="s">
+      <c r="A399" s="189" t="s">
         <v>1951</v>
       </c>
-      <c r="B399" s="186"/>
-      <c r="C399" s="186"/>
+      <c r="B399" s="189"/>
+      <c r="C399" s="189"/>
     </row>
     <row r="400" spans="1:3" ht="30">
       <c r="A400" s="23" t="s">
@@ -43377,11 +43627,11 @@
       <c r="C431" s="115"/>
     </row>
     <row r="432" spans="1:3">
-      <c r="A432" s="186" t="s">
+      <c r="A432" s="189" t="s">
         <v>2016</v>
       </c>
-      <c r="B432" s="186"/>
-      <c r="C432" s="186"/>
+      <c r="B432" s="189"/>
+      <c r="C432" s="189"/>
     </row>
     <row r="433" spans="1:2" ht="18">
       <c r="A433" s="43" t="s">
@@ -43928,11 +44178,11 @@
       </c>
     </row>
     <row r="513" spans="1:3">
-      <c r="A513" s="205" t="s">
+      <c r="A513" s="208" t="s">
         <v>2105</v>
       </c>
-      <c r="B513" s="205"/>
-      <c r="C513" s="205"/>
+      <c r="B513" s="208"/>
+      <c r="C513" s="208"/>
     </row>
     <row r="514" spans="1:3" ht="75">
       <c r="A514" s="115"/>
@@ -43942,11 +44192,11 @@
       <c r="C514" s="115"/>
     </row>
     <row r="515" spans="1:3">
-      <c r="A515" s="186" t="s">
+      <c r="A515" s="189" t="s">
         <v>2107</v>
       </c>
-      <c r="B515" s="186"/>
-      <c r="C515" s="186"/>
+      <c r="B515" s="189"/>
+      <c r="C515" s="189"/>
     </row>
     <row r="516" spans="1:3" ht="30">
       <c r="A516" s="123" t="s">
@@ -44039,11 +44289,11 @@
       <c r="C525" s="115"/>
     </row>
     <row r="528" spans="1:3">
-      <c r="A528" s="205" t="s">
+      <c r="A528" s="208" t="s">
         <v>2127</v>
       </c>
-      <c r="B528" s="205"/>
-      <c r="C528" s="205"/>
+      <c r="B528" s="208"/>
+      <c r="C528" s="208"/>
     </row>
     <row r="529" spans="1:3" ht="60">
       <c r="A529" s="115"/>
@@ -44053,11 +44303,11 @@
       <c r="C529" s="115"/>
     </row>
     <row r="530" spans="1:3">
-      <c r="A530" s="186" t="s">
+      <c r="A530" s="189" t="s">
         <v>2129</v>
       </c>
-      <c r="B530" s="186"/>
-      <c r="C530" s="186"/>
+      <c r="B530" s="189"/>
+      <c r="C530" s="189"/>
     </row>
     <row r="531" spans="1:3">
       <c r="A531" s="23" t="s">
@@ -44181,11 +44431,11 @@
       </c>
     </row>
     <row r="548" spans="1:3">
-      <c r="A548" s="186" t="s">
+      <c r="A548" s="189" t="s">
         <v>2158</v>
       </c>
-      <c r="B548" s="186"/>
-      <c r="C548" s="186"/>
+      <c r="B548" s="189"/>
+      <c r="C548" s="189"/>
     </row>
     <row r="549" spans="1:3">
       <c r="A549" s="115"/>
@@ -44340,11 +44590,11 @@
       <c r="C566" s="115"/>
     </row>
     <row r="567" spans="1:3">
-      <c r="A567" s="211" t="s">
+      <c r="A567" s="214" t="s">
         <v>2190</v>
       </c>
-      <c r="B567" s="211"/>
-      <c r="C567" s="211"/>
+      <c r="B567" s="214"/>
+      <c r="C567" s="214"/>
     </row>
     <row r="568" spans="1:3">
       <c r="A568" s="23" t="s">
@@ -44589,18 +44839,18 @@
       </c>
     </row>
     <row r="591" spans="1:3">
-      <c r="A591" s="205" t="s">
+      <c r="A591" s="208" t="s">
         <v>2248</v>
       </c>
-      <c r="B591" s="205"/>
-      <c r="C591" s="205"/>
+      <c r="B591" s="208"/>
+      <c r="C591" s="208"/>
     </row>
     <row r="593" spans="1:3">
-      <c r="A593" s="186" t="s">
+      <c r="A593" s="189" t="s">
         <v>2249</v>
       </c>
-      <c r="B593" s="186"/>
-      <c r="C593" s="186"/>
+      <c r="B593" s="189"/>
+      <c r="C593" s="189"/>
     </row>
     <row r="594" spans="1:3">
       <c r="A594" s="115" t="s">
@@ -44783,11 +45033,11 @@
       <c r="C617" s="115"/>
     </row>
     <row r="618" spans="1:3">
-      <c r="A618" s="205" t="s">
+      <c r="A618" s="208" t="s">
         <v>2280</v>
       </c>
-      <c r="B618" s="205"/>
-      <c r="C618" s="205"/>
+      <c r="B618" s="208"/>
+      <c r="C618" s="208"/>
     </row>
     <row r="619" spans="1:3" ht="75">
       <c r="A619" s="115"/>
@@ -44797,11 +45047,11 @@
       <c r="C619" s="115"/>
     </row>
     <row r="620" spans="1:3">
-      <c r="A620" s="186" t="s">
+      <c r="A620" s="189" t="s">
         <v>2282</v>
       </c>
-      <c r="B620" s="186"/>
-      <c r="C620" s="186"/>
+      <c r="B620" s="189"/>
+      <c r="C620" s="189"/>
     </row>
     <row r="621" spans="1:3" ht="30">
       <c r="A621" s="112" t="s">
@@ -44888,11 +45138,11 @@
       <c r="C630" s="115"/>
     </row>
     <row r="631" spans="1:3">
-      <c r="A631" s="186" t="s">
+      <c r="A631" s="189" t="s">
         <v>2300</v>
       </c>
-      <c r="B631" s="186"/>
-      <c r="C631" s="186"/>
+      <c r="B631" s="189"/>
+      <c r="C631" s="189"/>
     </row>
     <row r="632" spans="1:3">
       <c r="A632" s="23" t="s">
@@ -45359,11 +45609,11 @@
       <c r="C1" s="110"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="189" t="s">
+      <c r="A3" s="192" t="s">
         <v>2396</v>
       </c>
-      <c r="B3" s="189"/>
-      <c r="C3" s="189"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="192"/>
     </row>
     <row r="4" spans="1:3" ht="30">
       <c r="A4" s="112" t="s">
@@ -45375,11 +45625,11 @@
       <c r="C4" s="112"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="189" t="s">
+      <c r="A6" s="192" t="s">
         <v>2399</v>
       </c>
-      <c r="B6" s="189"/>
-      <c r="C6" s="189"/>
+      <c r="B6" s="192"/>
+      <c r="C6" s="192"/>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="112"/>
@@ -45450,18 +45700,18 @@
       <c r="C14" s="112"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="189" t="s">
+      <c r="A18" s="192" t="s">
         <v>2414</v>
       </c>
-      <c r="B18" s="189"/>
-      <c r="C18" s="189"/>
+      <c r="B18" s="192"/>
+      <c r="C18" s="192"/>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="188" t="s">
+      <c r="A20" s="191" t="s">
         <v>2415</v>
       </c>
-      <c r="B20" s="188"/>
-      <c r="C20" s="188"/>
+      <c r="B20" s="191"/>
+      <c r="C20" s="191"/>
     </row>
     <row r="21" spans="1:3" ht="30">
       <c r="A21" s="112"/>
@@ -45654,11 +45904,11 @@
       <c r="C44" s="112"/>
     </row>
     <row r="46" spans="1:3" s="85" customFormat="1">
-      <c r="A46" s="188" t="s">
+      <c r="A46" s="191" t="s">
         <v>2451</v>
       </c>
-      <c r="B46" s="188"/>
-      <c r="C46" s="188"/>
+      <c r="B46" s="191"/>
+      <c r="C46" s="191"/>
     </row>
     <row r="47" spans="1:3" s="85" customFormat="1">
       <c r="A47" s="112"/>
@@ -45728,11 +45978,11 @@
       <c r="C55" s="112"/>
     </row>
     <row r="56" spans="1:3" s="85" customFormat="1">
-      <c r="A56" s="188" t="s">
+      <c r="A56" s="191" t="s">
         <v>2463</v>
       </c>
-      <c r="B56" s="188"/>
-      <c r="C56" s="188"/>
+      <c r="B56" s="191"/>
+      <c r="C56" s="191"/>
     </row>
     <row r="57" spans="1:3" s="85" customFormat="1" ht="30">
       <c r="A57" s="112"/>
@@ -45859,11 +46109,11 @@
       <c r="C74" s="112"/>
     </row>
     <row r="75" spans="1:3" s="99" customFormat="1">
-      <c r="A75" s="188" t="s">
+      <c r="A75" s="191" t="s">
         <v>2481</v>
       </c>
-      <c r="B75" s="188"/>
-      <c r="C75" s="188"/>
+      <c r="B75" s="191"/>
+      <c r="C75" s="191"/>
     </row>
     <row r="76" spans="1:3" s="99" customFormat="1">
       <c r="A76" s="62"/>
@@ -45873,11 +46123,11 @@
       <c r="C76" s="112"/>
     </row>
     <row r="77" spans="1:3" s="99" customFormat="1">
-      <c r="A77" s="217" t="s">
+      <c r="A77" s="220" t="s">
         <v>2483</v>
       </c>
-      <c r="B77" s="217"/>
-      <c r="C77" s="217"/>
+      <c r="B77" s="220"/>
+      <c r="C77" s="220"/>
     </row>
     <row r="78" spans="1:3" s="99" customFormat="1">
       <c r="A78" s="62"/>
@@ -45932,11 +46182,11 @@
       <c r="C83" s="112"/>
     </row>
     <row r="84" spans="1:3" s="85" customFormat="1">
-      <c r="A84" s="217" t="s">
+      <c r="A84" s="220" t="s">
         <v>2495</v>
       </c>
-      <c r="B84" s="217"/>
-      <c r="C84" s="217"/>
+      <c r="B84" s="220"/>
+      <c r="C84" s="220"/>
     </row>
     <row r="85" spans="1:3" s="85" customFormat="1" ht="60">
       <c r="A85" s="112"/>
@@ -46000,11 +46250,11 @@
       <c r="C91" s="112"/>
     </row>
     <row r="92" spans="1:3">
-      <c r="A92" s="217" t="s">
+      <c r="A92" s="220" t="s">
         <v>2507</v>
       </c>
-      <c r="B92" s="217"/>
-      <c r="C92" s="217"/>
+      <c r="B92" s="220"/>
+      <c r="C92" s="220"/>
     </row>
     <row r="93" spans="1:3" s="101" customFormat="1" ht="120">
       <c r="A93" s="112"/>
@@ -46077,11 +46327,11 @@
       <c r="C100" s="112"/>
     </row>
     <row r="101" spans="1:3" s="101" customFormat="1">
-      <c r="A101" s="217" t="s">
+      <c r="A101" s="220" t="s">
         <v>2523</v>
       </c>
-      <c r="B101" s="217"/>
-      <c r="C101" s="217"/>
+      <c r="B101" s="220"/>
+      <c r="C101" s="220"/>
     </row>
     <row r="102" spans="1:3" s="101" customFormat="1" ht="75">
       <c r="A102" s="112"/>
@@ -46172,11 +46422,11 @@
       <c r="C111" s="112"/>
     </row>
     <row r="112" spans="1:3" s="101" customFormat="1">
-      <c r="A112" s="217" t="s">
+      <c r="A112" s="220" t="s">
         <v>2541</v>
       </c>
-      <c r="B112" s="217"/>
-      <c r="C112" s="217"/>
+      <c r="B112" s="220"/>
+      <c r="C112" s="220"/>
     </row>
     <row r="113" spans="1:3" s="101" customFormat="1" ht="90">
       <c r="A113" s="112"/>
@@ -46315,11 +46565,11 @@
       </c>
     </row>
     <row r="127" spans="1:3" s="101" customFormat="1">
-      <c r="A127" s="217" t="s">
+      <c r="A127" s="220" t="s">
         <v>2572</v>
       </c>
-      <c r="B127" s="217"/>
-      <c r="C127" s="217"/>
+      <c r="B127" s="220"/>
+      <c r="C127" s="220"/>
     </row>
     <row r="128" spans="1:3" s="101" customFormat="1" ht="75">
       <c r="A128" s="112"/>
@@ -46397,18 +46647,18 @@
       <c r="C136" s="112"/>
     </row>
     <row r="137" spans="1:3">
-      <c r="A137" s="189" t="s">
+      <c r="A137" s="192" t="s">
         <v>2587</v>
       </c>
-      <c r="B137" s="189"/>
-      <c r="C137" s="189"/>
+      <c r="B137" s="192"/>
+      <c r="C137" s="192"/>
     </row>
     <row r="139" spans="1:3">
-      <c r="A139" s="188" t="s">
+      <c r="A139" s="191" t="s">
         <v>2588</v>
       </c>
-      <c r="B139" s="188"/>
-      <c r="C139" s="188"/>
+      <c r="B139" s="191"/>
+      <c r="C139" s="191"/>
     </row>
     <row r="140" spans="1:3">
       <c r="A140" s="112"/>
@@ -46572,11 +46822,11 @@
       <c r="C158" s="112"/>
     </row>
     <row r="159" spans="1:3" s="93" customFormat="1">
-      <c r="A159" s="188" t="s">
+      <c r="A159" s="191" t="s">
         <v>2622</v>
       </c>
-      <c r="B159" s="188"/>
-      <c r="C159" s="188"/>
+      <c r="B159" s="191"/>
+      <c r="C159" s="191"/>
     </row>
     <row r="160" spans="1:3" s="93" customFormat="1">
       <c r="A160" s="112"/>
@@ -46953,11 +47203,11 @@
     </row>
     <row r="207" spans="1:3" s="138" customFormat="1"/>
     <row r="209" spans="1:3">
-      <c r="A209" s="212" t="s">
+      <c r="A209" s="215" t="s">
         <v>2648</v>
       </c>
-      <c r="B209" s="212"/>
-      <c r="C209" s="212"/>
+      <c r="B209" s="215"/>
+      <c r="C209" s="215"/>
     </row>
     <row r="210" spans="1:3" ht="60">
       <c r="A210" s="112"/>
@@ -46983,11 +47233,11 @@
       <c r="C212" s="112"/>
     </row>
     <row r="215" spans="1:3">
-      <c r="A215" s="188" t="s">
+      <c r="A215" s="191" t="s">
         <v>2652</v>
       </c>
-      <c r="B215" s="188"/>
-      <c r="C215" s="188"/>
+      <c r="B215" s="191"/>
+      <c r="C215" s="191"/>
     </row>
     <row r="216" spans="1:3">
       <c r="A216" s="112" t="s">
@@ -47059,11 +47309,11 @@
       <c r="C226" s="112"/>
     </row>
     <row r="228" spans="1:3">
-      <c r="A228" s="192" t="s">
+      <c r="A228" s="195" t="s">
         <v>2655</v>
       </c>
-      <c r="B228" s="192"/>
-      <c r="C228" s="192"/>
+      <c r="B228" s="195"/>
+      <c r="C228" s="195"/>
     </row>
     <row r="230" spans="1:3" ht="30">
       <c r="A230" s="90" t="s">
@@ -47278,18 +47528,18 @@
       <c r="C254" s="112"/>
     </row>
     <row r="256" spans="1:3">
-      <c r="A256" s="189" t="s">
+      <c r="A256" s="192" t="s">
         <v>2704</v>
       </c>
-      <c r="B256" s="189"/>
-      <c r="C256" s="189"/>
+      <c r="B256" s="192"/>
+      <c r="C256" s="192"/>
     </row>
     <row r="259" spans="1:3">
-      <c r="A259" s="188" t="s">
+      <c r="A259" s="191" t="s">
         <v>2705</v>
       </c>
-      <c r="B259" s="188"/>
-      <c r="C259" s="188"/>
+      <c r="B259" s="191"/>
+      <c r="C259" s="191"/>
     </row>
     <row r="260" spans="1:3" ht="75">
       <c r="A260" s="112"/>
@@ -47482,11 +47732,11 @@
     <row r="290" spans="1:3" s="143" customFormat="1"/>
     <row r="291" spans="1:3" s="143" customFormat="1"/>
     <row r="293" spans="1:3" s="106" customFormat="1">
-      <c r="A293" s="188" t="s">
+      <c r="A293" s="191" t="s">
         <v>2731</v>
       </c>
-      <c r="B293" s="188"/>
-      <c r="C293" s="188"/>
+      <c r="B293" s="191"/>
+      <c r="C293" s="191"/>
     </row>
     <row r="294" spans="1:3" s="106" customFormat="1">
       <c r="A294" s="112"/>
@@ -47594,11 +47844,11 @@
       <c r="C306" s="112"/>
     </row>
     <row r="307" spans="1:3" s="144" customFormat="1">
-      <c r="A307" s="188" t="s">
+      <c r="A307" s="191" t="s">
         <v>4189</v>
       </c>
-      <c r="B307" s="188"/>
-      <c r="C307" s="188"/>
+      <c r="B307" s="191"/>
+      <c r="C307" s="191"/>
     </row>
     <row r="308" spans="1:3" s="144" customFormat="1"/>
     <row r="309" spans="1:3" s="144" customFormat="1">
@@ -47778,11 +48028,11 @@
       </c>
     </row>
     <row r="333" spans="1:3" s="146" customFormat="1">
-      <c r="A333" s="213" t="s">
+      <c r="A333" s="216" t="s">
         <v>4259</v>
       </c>
-      <c r="B333" s="214"/>
-      <c r="C333" s="214"/>
+      <c r="B333" s="217"/>
+      <c r="C333" s="217"/>
     </row>
     <row r="334" spans="1:3" s="146" customFormat="1">
       <c r="A334" s="151"/>
@@ -47791,11 +48041,11 @@
       </c>
     </row>
     <row r="335" spans="1:3" s="146" customFormat="1">
-      <c r="A335" s="215" t="s">
+      <c r="A335" s="218" t="s">
         <v>4261</v>
       </c>
-      <c r="B335" s="216"/>
-      <c r="C335" s="216"/>
+      <c r="B335" s="219"/>
+      <c r="C335" s="219"/>
     </row>
     <row r="336" spans="1:3" s="146" customFormat="1">
       <c r="A336" s="156" t="s">
@@ -47952,11 +48202,11 @@
       </c>
     </row>
     <row r="356" spans="1:3">
-      <c r="A356" s="189" t="s">
+      <c r="A356" s="192" t="s">
         <v>2750</v>
       </c>
-      <c r="B356" s="189"/>
-      <c r="C356" s="189"/>
+      <c r="B356" s="192"/>
+      <c r="C356" s="192"/>
     </row>
     <row r="359" spans="1:3">
       <c r="A359" s="121" t="s">
@@ -48034,11 +48284,11 @@
       <c r="C367" s="112"/>
     </row>
     <row r="369" spans="1:3">
-      <c r="A369" s="188" t="s">
+      <c r="A369" s="191" t="s">
         <v>2765</v>
       </c>
-      <c r="B369" s="188"/>
-      <c r="C369" s="188"/>
+      <c r="B369" s="191"/>
+      <c r="C369" s="191"/>
     </row>
     <row r="370" spans="1:3" ht="30">
       <c r="A370" s="112"/>
@@ -48113,11 +48363,11 @@
       <c r="C378" s="112"/>
     </row>
     <row r="379" spans="1:3">
-      <c r="A379" s="188" t="s">
+      <c r="A379" s="191" t="s">
         <v>2782</v>
       </c>
-      <c r="B379" s="188"/>
-      <c r="C379" s="188"/>
+      <c r="B379" s="191"/>
+      <c r="C379" s="191"/>
     </row>
     <row r="380" spans="1:3">
       <c r="A380" s="112"/>
@@ -48233,18 +48483,18 @@
       <c r="C393" s="112"/>
     </row>
     <row r="395" spans="1:3">
-      <c r="A395" s="189" t="s">
+      <c r="A395" s="192" t="s">
         <v>2805</v>
       </c>
-      <c r="B395" s="189"/>
-      <c r="C395" s="189"/>
+      <c r="B395" s="192"/>
+      <c r="C395" s="192"/>
     </row>
     <row r="398" spans="1:3">
-      <c r="A398" s="188" t="s">
+      <c r="A398" s="191" t="s">
         <v>2806</v>
       </c>
-      <c r="B398" s="188"/>
-      <c r="C398" s="188"/>
+      <c r="B398" s="191"/>
+      <c r="C398" s="191"/>
     </row>
     <row r="399" spans="1:3" ht="75">
       <c r="A399" s="112"/>
@@ -48359,11 +48609,11 @@
       <c r="C412" s="112"/>
     </row>
     <row r="415" spans="1:3">
-      <c r="A415" s="189" t="s">
+      <c r="A415" s="192" t="s">
         <v>3864</v>
       </c>
-      <c r="B415" s="189"/>
-      <c r="C415" s="189"/>
+      <c r="B415" s="192"/>
+      <c r="C415" s="192"/>
     </row>
     <row r="416" spans="1:3" ht="30">
       <c r="B416" s="10" t="s">
@@ -48371,11 +48621,11 @@
       </c>
     </row>
     <row r="417" spans="1:3">
-      <c r="A417" s="188" t="s">
+      <c r="A417" s="191" t="s">
         <v>3866</v>
       </c>
-      <c r="B417" s="188"/>
-      <c r="C417" s="188"/>
+      <c r="B417" s="191"/>
+      <c r="C417" s="191"/>
     </row>
     <row r="418" spans="1:3">
       <c r="B418" s="10" t="s">
@@ -48407,11 +48657,11 @@
     </row>
     <row r="423" spans="1:3" s="127" customFormat="1"/>
     <row r="425" spans="1:3">
-      <c r="A425" s="188" t="s">
+      <c r="A425" s="191" t="s">
         <v>3872</v>
       </c>
-      <c r="B425" s="188"/>
-      <c r="C425" s="188"/>
+      <c r="B425" s="191"/>
+      <c r="C425" s="191"/>
     </row>
     <row r="426" spans="1:3" ht="60">
       <c r="B426" s="10" t="s">
@@ -48516,11 +48766,11 @@
       </c>
     </row>
     <row r="441" spans="1:3" s="171" customFormat="1">
-      <c r="A441" s="188" t="s">
+      <c r="A441" s="191" t="s">
         <v>4432</v>
       </c>
-      <c r="B441" s="188"/>
-      <c r="C441" s="188"/>
+      <c r="B441" s="191"/>
+      <c r="C441" s="191"/>
     </row>
     <row r="442" spans="1:3" s="171" customFormat="1">
       <c r="B442" s="171" t="s">
@@ -48638,11 +48888,11 @@
       </c>
     </row>
     <row r="459" spans="1:3" s="171" customFormat="1">
-      <c r="A459" s="188" t="s">
+      <c r="A459" s="191" t="s">
         <v>4459</v>
       </c>
-      <c r="B459" s="188"/>
-      <c r="C459" s="188"/>
+      <c r="B459" s="191"/>
+      <c r="C459" s="191"/>
     </row>
     <row r="460" spans="1:3" s="174" customFormat="1" ht="30">
       <c r="B460" s="174" t="s">
@@ -48720,18 +48970,18 @@
     <row r="473" spans="1:3" s="174" customFormat="1"/>
     <row r="474" spans="1:3" s="174" customFormat="1"/>
     <row r="476" spans="1:3">
-      <c r="A476" s="189" t="s">
+      <c r="A476" s="192" t="s">
         <v>4396</v>
       </c>
-      <c r="B476" s="189"/>
-      <c r="C476" s="189"/>
+      <c r="B476" s="192"/>
+      <c r="C476" s="192"/>
     </row>
     <row r="478" spans="1:3">
-      <c r="A478" s="188" t="s">
+      <c r="A478" s="191" t="s">
         <v>4397</v>
       </c>
-      <c r="B478" s="188"/>
-      <c r="C478" s="188"/>
+      <c r="B478" s="191"/>
+      <c r="C478" s="191"/>
     </row>
     <row r="479" spans="1:3">
       <c r="B479" s="10" t="s">
@@ -48957,11 +49207,11 @@
       <c r="C1" s="110"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="188" t="s">
+      <c r="A3" s="191" t="s">
         <v>2828</v>
       </c>
-      <c r="B3" s="188"/>
-      <c r="C3" s="188"/>
+      <c r="B3" s="191"/>
+      <c r="C3" s="191"/>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="121" t="s">
@@ -49005,7 +49255,7 @@
       <c r="C9" s="112"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="218" t="s">
+      <c r="A10" s="221" t="s">
         <v>2836</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -49014,21 +49264,21 @@
       <c r="C10" s="112"/>
     </row>
     <row r="11" spans="1:3" ht="30">
-      <c r="A11" s="218"/>
+      <c r="A11" s="221"/>
       <c r="B11" s="4" t="s">
         <v>2838</v>
       </c>
       <c r="C11" s="112"/>
     </row>
     <row r="12" spans="1:3" ht="30">
-      <c r="A12" s="218"/>
+      <c r="A12" s="221"/>
       <c r="B12" s="4" t="s">
         <v>2839</v>
       </c>
       <c r="C12" s="112"/>
     </row>
     <row r="13" spans="1:3" ht="30">
-      <c r="A13" s="218" t="s">
+      <c r="A13" s="221" t="s">
         <v>2840</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -49037,14 +49287,14 @@
       <c r="C13" s="112"/>
     </row>
     <row r="14" spans="1:3" ht="30">
-      <c r="A14" s="218"/>
+      <c r="A14" s="221"/>
       <c r="B14" s="4" t="s">
         <v>2842</v>
       </c>
       <c r="C14" s="112"/>
     </row>
     <row r="15" spans="1:3" ht="30">
-      <c r="A15" s="218" t="s">
+      <c r="A15" s="221" t="s">
         <v>2843</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -49053,14 +49303,14 @@
       <c r="C15" s="112"/>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="218"/>
+      <c r="A16" s="221"/>
       <c r="B16" s="4" t="s">
         <v>2845</v>
       </c>
       <c r="C16" s="112"/>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="218" t="s">
+      <c r="A17" s="221" t="s">
         <v>2846</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -49068,43 +49318,43 @@
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="218"/>
+      <c r="A18" s="221"/>
       <c r="B18" s="4" t="s">
         <v>2848</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="218"/>
+      <c r="A19" s="221"/>
       <c r="B19" s="122" t="s">
         <v>2849</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="218"/>
+      <c r="A20" s="221"/>
       <c r="B20" s="122" t="s">
         <v>2850</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="218"/>
+      <c r="A21" s="221"/>
       <c r="B21" s="122" t="s">
         <v>2851</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="218"/>
+      <c r="A22" s="221"/>
       <c r="B22" s="4" t="s">
         <v>2852</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="218"/>
+      <c r="A23" s="221"/>
       <c r="B23" s="4" t="s">
         <v>2853</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="218" t="s">
+      <c r="A24" s="221" t="s">
         <v>2854</v>
       </c>
       <c r="B24" s="4" t="s">
@@ -49112,13 +49362,13 @@
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="218"/>
+      <c r="A25" s="221"/>
       <c r="B25" s="4" t="s">
         <v>2856</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="218" t="s">
+      <c r="A26" s="221" t="s">
         <v>2857</v>
       </c>
       <c r="B26" s="4" t="s">
@@ -49126,13 +49376,13 @@
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="218"/>
+      <c r="A27" s="221"/>
       <c r="B27" s="55" t="s">
         <v>2859</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="218"/>
+      <c r="A28" s="221"/>
       <c r="B28" s="4" t="s">
         <v>2860</v>
       </c>
@@ -49144,7 +49394,7 @@
       <c r="B29" s="112"/>
     </row>
     <row r="30" spans="1:2" ht="30">
-      <c r="A30" s="219" t="s">
+      <c r="A30" s="222" t="s">
         <v>2862</v>
       </c>
       <c r="B30" s="112" t="s">
@@ -49152,13 +49402,13 @@
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="219"/>
+      <c r="A31" s="222"/>
       <c r="B31" s="112" t="s">
         <v>2864</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="30">
-      <c r="A32" s="219" t="s">
+      <c r="A32" s="222" t="s">
         <v>2859</v>
       </c>
       <c r="B32" s="112" t="s">
@@ -49166,13 +49416,13 @@
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="219"/>
+      <c r="A33" s="222"/>
       <c r="B33" s="112" t="s">
         <v>2866</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="30">
-      <c r="A34" s="219" t="s">
+      <c r="A34" s="222" t="s">
         <v>2867</v>
       </c>
       <c r="B34" s="112" t="s">
@@ -49180,13 +49430,13 @@
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="219"/>
+      <c r="A35" s="222"/>
       <c r="B35" s="112" t="s">
         <v>2869</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="30">
-      <c r="A36" s="219" t="s">
+      <c r="A36" s="222" t="s">
         <v>2870</v>
       </c>
       <c r="B36" s="112" t="s">
@@ -49194,13 +49444,13 @@
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="219"/>
+      <c r="A37" s="222"/>
       <c r="B37" s="112" t="s">
         <v>2872</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="30">
-      <c r="A38" s="219" t="s">
+      <c r="A38" s="222" t="s">
         <v>2873</v>
       </c>
       <c r="B38" s="112" t="s">
@@ -49208,13 +49458,13 @@
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="219"/>
+      <c r="A39" s="222"/>
       <c r="B39" s="112" t="s">
         <v>2875</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="30">
-      <c r="A40" s="219" t="s">
+      <c r="A40" s="222" t="s">
         <v>2876</v>
       </c>
       <c r="B40" s="112" t="s">
@@ -49222,13 +49472,13 @@
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="219"/>
+      <c r="A41" s="222"/>
       <c r="B41" s="112" t="s">
         <v>2878</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="30">
-      <c r="A42" s="219" t="s">
+      <c r="A42" s="222" t="s">
         <v>2879</v>
       </c>
       <c r="B42" s="112" t="s">
@@ -49236,13 +49486,13 @@
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="219"/>
+      <c r="A43" s="222"/>
       <c r="B43" s="112" t="s">
         <v>2881</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="219" t="s">
+      <c r="A44" s="222" t="s">
         <v>2882</v>
       </c>
       <c r="B44" s="112" t="s">
@@ -49250,13 +49500,13 @@
       </c>
     </row>
     <row r="45" spans="1:2" ht="40.5">
-      <c r="A45" s="219"/>
+      <c r="A45" s="222"/>
       <c r="B45" s="112" t="s">
         <v>2884</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="219" t="s">
+      <c r="A46" s="222" t="s">
         <v>2885</v>
       </c>
       <c r="B46" s="112" t="s">
@@ -49264,13 +49514,13 @@
       </c>
     </row>
     <row r="47" spans="1:2" ht="27.75">
-      <c r="A47" s="219"/>
+      <c r="A47" s="222"/>
       <c r="B47" s="112" t="s">
         <v>2887</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="219" t="s">
+      <c r="A48" s="222" t="s">
         <v>2888</v>
       </c>
       <c r="B48" s="112" t="s">
@@ -49278,13 +49528,13 @@
       </c>
     </row>
     <row r="49" spans="1:2" ht="27.75">
-      <c r="A49" s="219"/>
+      <c r="A49" s="222"/>
       <c r="B49" s="112" t="s">
         <v>2890</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="219" t="s">
+      <c r="A50" s="222" t="s">
         <v>2891</v>
       </c>
       <c r="B50" s="112" t="s">
@@ -49292,13 +49542,13 @@
       </c>
     </row>
     <row r="51" spans="1:2" ht="40.5">
-      <c r="A51" s="219"/>
+      <c r="A51" s="222"/>
       <c r="B51" s="112" t="s">
         <v>2893</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="219" t="s">
+      <c r="A52" s="222" t="s">
         <v>2894</v>
       </c>
       <c r="B52" s="112" t="s">
@@ -49306,13 +49556,13 @@
       </c>
     </row>
     <row r="53" spans="1:2" ht="40.5">
-      <c r="A53" s="219"/>
+      <c r="A53" s="222"/>
       <c r="B53" s="112" t="s">
         <v>2896</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="30">
-      <c r="A54" s="219" t="s">
+      <c r="A54" s="222" t="s">
         <v>2897</v>
       </c>
       <c r="B54" s="112" t="s">
@@ -49320,13 +49570,13 @@
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="219"/>
+      <c r="A55" s="222"/>
       <c r="B55" s="112" t="s">
         <v>2899</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="30">
-      <c r="A56" s="219" t="s">
+      <c r="A56" s="222" t="s">
         <v>2900</v>
       </c>
       <c r="B56" s="112" t="s">
@@ -49334,13 +49584,13 @@
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="219"/>
+      <c r="A57" s="222"/>
       <c r="B57" s="112" t="s">
         <v>2902</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="30">
-      <c r="A58" s="219" t="s">
+      <c r="A58" s="222" t="s">
         <v>2903</v>
       </c>
       <c r="B58" s="112" t="s">
@@ -49348,13 +49598,13 @@
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="219"/>
+      <c r="A59" s="222"/>
       <c r="B59" s="112" t="s">
         <v>2905</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="219" t="s">
+      <c r="A60" s="222" t="s">
         <v>2906</v>
       </c>
       <c r="B60" s="112" t="s">
@@ -49362,13 +49612,13 @@
       </c>
     </row>
     <row r="61" spans="1:2" ht="27.75">
-      <c r="A61" s="219"/>
+      <c r="A61" s="222"/>
       <c r="B61" s="112" t="s">
         <v>2908</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="219" t="s">
+      <c r="A62" s="222" t="s">
         <v>2909</v>
       </c>
       <c r="B62" s="112" t="s">
@@ -49376,13 +49626,13 @@
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="219"/>
+      <c r="A63" s="222"/>
       <c r="B63" s="112" t="s">
         <v>2911</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="30">
-      <c r="A64" s="219" t="s">
+      <c r="A64" s="222" t="s">
         <v>2912</v>
       </c>
       <c r="B64" s="112" t="s">
@@ -49390,25 +49640,25 @@
       </c>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="219"/>
+      <c r="A65" s="222"/>
       <c r="B65" s="112" t="s">
         <v>2914</v>
       </c>
       <c r="C65" s="112"/>
     </row>
     <row r="67" spans="1:3">
-      <c r="A67" s="189" t="s">
+      <c r="A67" s="192" t="s">
         <v>2915</v>
       </c>
-      <c r="B67" s="189"/>
-      <c r="C67" s="189"/>
+      <c r="B67" s="192"/>
+      <c r="C67" s="192"/>
     </row>
     <row r="68" spans="1:3">
-      <c r="A68" s="188" t="s">
+      <c r="A68" s="191" t="s">
         <v>2916</v>
       </c>
-      <c r="B68" s="188"/>
-      <c r="C68" s="188"/>
+      <c r="B68" s="191"/>
+      <c r="C68" s="191"/>
     </row>
     <row r="69" spans="1:3" ht="30">
       <c r="A69" s="112"/>
@@ -49418,11 +49668,11 @@
       <c r="C69" s="112"/>
     </row>
     <row r="70" spans="1:3">
-      <c r="A70" s="192" t="s">
+      <c r="A70" s="195" t="s">
         <v>2918</v>
       </c>
-      <c r="B70" s="192"/>
-      <c r="C70" s="192"/>
+      <c r="B70" s="195"/>
+      <c r="C70" s="195"/>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="121" t="s">
@@ -49574,11 +49824,11 @@
       <c r="C89" s="112"/>
     </row>
     <row r="91" spans="1:3">
-      <c r="A91" s="192" t="s">
+      <c r="A91" s="195" t="s">
         <v>2950</v>
       </c>
-      <c r="B91" s="192"/>
-      <c r="C91" s="192"/>
+      <c r="B91" s="195"/>
+      <c r="C91" s="195"/>
     </row>
     <row r="93" spans="1:3">
       <c r="A93" s="121" t="s">
@@ -49857,11 +50107,11 @@
       <c r="C134" s="112"/>
     </row>
     <row r="135" spans="1:3">
-      <c r="A135" s="192" t="s">
+      <c r="A135" s="195" t="s">
         <v>3010</v>
       </c>
-      <c r="B135" s="192"/>
-      <c r="C135" s="192"/>
+      <c r="B135" s="195"/>
+      <c r="C135" s="195"/>
     </row>
     <row r="136" spans="1:3" ht="30">
       <c r="A136" s="112" t="s">
@@ -50176,18 +50426,18 @@
       <c r="C187" s="112"/>
     </row>
     <row r="189" spans="1:3">
-      <c r="A189" s="188" t="s">
+      <c r="A189" s="191" t="s">
         <v>3074</v>
       </c>
-      <c r="B189" s="188"/>
-      <c r="C189" s="188"/>
+      <c r="B189" s="191"/>
+      <c r="C189" s="191"/>
     </row>
     <row r="190" spans="1:3">
-      <c r="A190" s="192" t="s">
+      <c r="A190" s="195" t="s">
         <v>3075</v>
       </c>
-      <c r="B190" s="192"/>
-      <c r="C190" s="192"/>
+      <c r="B190" s="195"/>
+      <c r="C190" s="195"/>
     </row>
     <row r="192" spans="1:3">
       <c r="A192" s="121" t="s">
@@ -50369,11 +50619,11 @@
       <c r="C218" s="112"/>
     </row>
     <row r="221" spans="1:3">
-      <c r="A221" s="192" t="s">
+      <c r="A221" s="195" t="s">
         <v>3113</v>
       </c>
-      <c r="B221" s="192"/>
-      <c r="C221" s="192"/>
+      <c r="B221" s="195"/>
+      <c r="C221" s="195"/>
     </row>
     <row r="222" spans="1:3">
       <c r="A222" s="112" t="s">
@@ -50687,25 +50937,25 @@
       <c r="C260" s="112"/>
     </row>
     <row r="263" spans="1:3">
-      <c r="A263" s="212" t="s">
+      <c r="A263" s="215" t="s">
         <v>3172</v>
       </c>
-      <c r="B263" s="212"/>
-      <c r="C263" s="212"/>
+      <c r="B263" s="215"/>
+      <c r="C263" s="215"/>
     </row>
     <row r="265" spans="1:3">
-      <c r="A265" s="188" t="s">
+      <c r="A265" s="191" t="s">
         <v>3173</v>
       </c>
-      <c r="B265" s="188"/>
-      <c r="C265" s="188"/>
+      <c r="B265" s="191"/>
+      <c r="C265" s="191"/>
     </row>
     <row r="267" spans="1:3">
-      <c r="A267" s="192" t="s">
+      <c r="A267" s="195" t="s">
         <v>3174</v>
       </c>
-      <c r="B267" s="192"/>
-      <c r="C267" s="192"/>
+      <c r="B267" s="195"/>
+      <c r="C267" s="195"/>
     </row>
     <row r="269" spans="1:3">
       <c r="A269" s="112" t="s">
@@ -50861,7 +51111,7 @@
       <c r="A288" s="25" t="s">
         <v>3210</v>
       </c>
-      <c r="B288" s="190" t="s">
+      <c r="B288" s="193" t="s">
         <v>3211</v>
       </c>
     </row>
@@ -50869,15 +51119,15 @@
       <c r="A289" s="25" t="s">
         <v>3212</v>
       </c>
-      <c r="B289" s="190"/>
+      <c r="B289" s="193"/>
       <c r="C289" s="112"/>
     </row>
     <row r="290" spans="1:3">
-      <c r="A290" s="192" t="s">
+      <c r="A290" s="195" t="s">
         <v>3213</v>
       </c>
-      <c r="B290" s="192"/>
-      <c r="C290" s="192"/>
+      <c r="B290" s="195"/>
+      <c r="C290" s="195"/>
     </row>
     <row r="292" spans="1:3">
       <c r="A292" s="25" t="s">
@@ -50925,11 +51175,11 @@
       <c r="C296" s="112"/>
     </row>
     <row r="301" spans="1:3">
-      <c r="A301" s="189" t="s">
+      <c r="A301" s="192" t="s">
         <v>3222</v>
       </c>
-      <c r="B301" s="189"/>
-      <c r="C301" s="189"/>
+      <c r="B301" s="192"/>
+      <c r="C301" s="192"/>
     </row>
     <row r="302" spans="1:3">
       <c r="A302" s="112"/>
@@ -50939,11 +51189,11 @@
       <c r="C302" s="112"/>
     </row>
     <row r="303" spans="1:3">
-      <c r="A303" s="188" t="s">
+      <c r="A303" s="191" t="s">
         <v>3224</v>
       </c>
-      <c r="B303" s="188"/>
-      <c r="C303" s="188"/>
+      <c r="B303" s="191"/>
+      <c r="C303" s="191"/>
     </row>
     <row r="305" spans="1:2">
       <c r="A305" s="121" t="s">
@@ -51042,18 +51292,18 @@
       </c>
     </row>
     <row r="321" spans="1:3">
-      <c r="A321" s="189" t="s">
+      <c r="A321" s="192" t="s">
         <v>3240</v>
       </c>
-      <c r="B321" s="189"/>
-      <c r="C321" s="189"/>
+      <c r="B321" s="192"/>
+      <c r="C321" s="192"/>
     </row>
     <row r="323" spans="1:3">
-      <c r="A323" s="188" t="s">
+      <c r="A323" s="191" t="s">
         <v>3241</v>
       </c>
-      <c r="B323" s="188"/>
-      <c r="C323" s="188"/>
+      <c r="B323" s="191"/>
+      <c r="C323" s="191"/>
     </row>
     <row r="325" spans="1:3" ht="210">
       <c r="A325" s="121" t="s">
@@ -51426,18 +51676,18 @@
       <c r="C372" s="112"/>
     </row>
     <row r="374" spans="1:3">
-      <c r="A374" s="189" t="s">
+      <c r="A374" s="192" t="s">
         <v>3301</v>
       </c>
-      <c r="B374" s="189"/>
-      <c r="C374" s="189"/>
+      <c r="B374" s="192"/>
+      <c r="C374" s="192"/>
     </row>
     <row r="376" spans="1:3">
-      <c r="A376" s="188" t="s">
+      <c r="A376" s="191" t="s">
         <v>3302</v>
       </c>
-      <c r="B376" s="188"/>
-      <c r="C376" s="188"/>
+      <c r="B376" s="191"/>
+      <c r="C376" s="191"/>
     </row>
     <row r="377" spans="1:3" ht="45">
       <c r="A377" s="112"/>
@@ -51670,11 +51920,11 @@
       <c r="C406" s="112"/>
     </row>
     <row r="409" spans="1:3">
-      <c r="A409" s="188" t="s">
+      <c r="A409" s="191" t="s">
         <v>3337</v>
       </c>
-      <c r="B409" s="188"/>
-      <c r="C409" s="188"/>
+      <c r="B409" s="191"/>
+      <c r="C409" s="191"/>
     </row>
     <row r="410" spans="1:3" ht="30">
       <c r="A410" s="112"/>
@@ -51756,11 +52006,11 @@
       <c r="C418" s="112"/>
     </row>
     <row r="421" spans="1:3">
-      <c r="A421" s="189" t="s">
+      <c r="A421" s="192" t="s">
         <v>3355</v>
       </c>
-      <c r="B421" s="189"/>
-      <c r="C421" s="189"/>
+      <c r="B421" s="192"/>
+      <c r="C421" s="192"/>
     </row>
     <row r="422" spans="1:3" ht="75">
       <c r="A422" s="112"/>
@@ -51982,11 +52232,11 @@
       <c r="C448" s="112"/>
     </row>
     <row r="450" spans="1:3">
-      <c r="A450" s="189" t="s">
+      <c r="A450" s="192" t="s">
         <v>1671</v>
       </c>
-      <c r="B450" s="189"/>
-      <c r="C450" s="189"/>
+      <c r="B450" s="192"/>
+      <c r="C450" s="192"/>
     </row>
     <row r="451" spans="1:3" ht="45">
       <c r="A451" s="112"/>
@@ -51996,11 +52246,11 @@
       <c r="C451" s="112"/>
     </row>
     <row r="452" spans="1:3">
-      <c r="A452" s="188" t="s">
+      <c r="A452" s="191" t="s">
         <v>3399</v>
       </c>
-      <c r="B452" s="188"/>
-      <c r="C452" s="188"/>
+      <c r="B452" s="191"/>
+      <c r="C452" s="191"/>
     </row>
     <row r="454" spans="1:3" s="58" customFormat="1">
       <c r="A454" s="121" t="s">
@@ -52348,11 +52598,11 @@
       <c r="C494" s="112"/>
     </row>
     <row r="495" spans="1:3">
-      <c r="A495" s="188" t="s">
+      <c r="A495" s="191" t="s">
         <v>3469</v>
       </c>
-      <c r="B495" s="188"/>
-      <c r="C495" s="188"/>
+      <c r="B495" s="191"/>
+      <c r="C495" s="191"/>
     </row>
     <row r="497" spans="1:3">
       <c r="A497" s="121" t="s">
@@ -52428,11 +52678,11 @@
       <c r="C505" s="112"/>
     </row>
     <row r="507" spans="1:3">
-      <c r="A507" s="188" t="s">
+      <c r="A507" s="191" t="s">
         <v>3481</v>
       </c>
-      <c r="B507" s="188"/>
-      <c r="C507" s="188"/>
+      <c r="B507" s="191"/>
+      <c r="C507" s="191"/>
     </row>
     <row r="508" spans="1:3" ht="30">
       <c r="A508" s="112"/>
@@ -52528,11 +52778,11 @@
       <c r="C518" s="112"/>
     </row>
     <row r="520" spans="1:3">
-      <c r="A520" s="188" t="s">
+      <c r="A520" s="191" t="s">
         <v>3496</v>
       </c>
-      <c r="B520" s="188"/>
-      <c r="C520" s="188"/>
+      <c r="B520" s="191"/>
+      <c r="C520" s="191"/>
     </row>
     <row r="521" spans="1:3" ht="30">
       <c r="A521" s="112"/>
@@ -52680,11 +52930,11 @@
       <c r="C537" s="112"/>
     </row>
     <row r="538" spans="1:3">
-      <c r="A538" s="212" t="s">
+      <c r="A538" s="215" t="s">
         <v>3517</v>
       </c>
-      <c r="B538" s="212"/>
-      <c r="C538" s="212"/>
+      <c r="B538" s="215"/>
+      <c r="C538" s="215"/>
     </row>
     <row r="539" spans="1:3" ht="45">
       <c r="A539" s="112"/>
@@ -52791,11 +53041,11 @@
       <c r="C550" s="112"/>
     </row>
     <row r="552" spans="1:3">
-      <c r="A552" s="189" t="s">
+      <c r="A552" s="192" t="s">
         <v>3540</v>
       </c>
-      <c r="B552" s="189"/>
-      <c r="C552" s="189"/>
+      <c r="B552" s="192"/>
+      <c r="C552" s="192"/>
     </row>
     <row r="553" spans="1:3" ht="75">
       <c r="A553" s="112"/>
@@ -52805,11 +53055,11 @@
       <c r="C553" s="112"/>
     </row>
     <row r="554" spans="1:3">
-      <c r="A554" s="188" t="s">
+      <c r="A554" s="191" t="s">
         <v>3542</v>
       </c>
-      <c r="B554" s="188"/>
-      <c r="C554" s="188"/>
+      <c r="B554" s="191"/>
+      <c r="C554" s="191"/>
     </row>
     <row r="555" spans="1:3">
       <c r="A555" s="112"/>
@@ -53221,11 +53471,11 @@
       <c r="C605" s="112"/>
     </row>
     <row r="607" spans="1:3">
-      <c r="A607" s="188" t="s">
+      <c r="A607" s="191" t="s">
         <v>3609</v>
       </c>
-      <c r="B607" s="188"/>
-      <c r="C607" s="188"/>
+      <c r="B607" s="191"/>
+      <c r="C607" s="191"/>
     </row>
     <row r="608" spans="1:3" ht="135">
       <c r="A608" s="112"/>
